--- a/excel-files/LAS PINAS/ALMANZA ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/LAS PINAS/ALMANZA ELEMENTARY SCHOOL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="778" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A43ACC8-6753-4AB5-A54B-872909AEFA75}"/>
+  <xr:revisionPtr revIDLastSave="903" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC243086-1756-4730-BA32-A0219B7FA692}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="93">
   <si>
     <t>Grade Level</t>
   </si>
@@ -206,9 +206,6 @@
   </si>
   <si>
     <t>GAP - LAS - Q3</t>
-  </si>
-  <si>
-    <t>SURPLUS - LAS - Q3</t>
   </si>
   <si>
     <t>Quantity based on Target LAS - Q4</t>
@@ -508,7 +505,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -633,24 +630,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -767,19 +751,6 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -796,7 +767,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="62">
     <dxf>
       <font>
         <b/>
@@ -2234,45 +2205,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -3057,7 +2989,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="61" headerRowBorderDxfId="59" tableBorderDxfId="60">
   <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
@@ -3074,43 +3006,40 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
-  <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
-  <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{945324E6-140A-476C-A8C3-23A16D4D262F}" name="Enrolment S.Y. 2025-2026 " dataDxfId="54"/>
-    <tableColumn id="4" xr3:uid="{A2D4C0AF-3699-4D3C-A791-2D7D8004CC89}" name="Quantity based on Target LAS - Q1 " dataDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:Z135" totalsRowShown="0" dataDxfId="58" headerRowBorderDxfId="56" tableBorderDxfId="57">
+  <autoFilter ref="A2:Z135" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
+  <tableColumns count="26">
+    <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{945324E6-140A-476C-A8C3-23A16D4D262F}" name="Enrolment S.Y. 2025-2026 " dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{A2D4C0AF-3699-4D3C-A791-2D7D8004CC89}" name="Quantity based on Target LAS - Q1 " dataDxfId="52">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9CE2D7B1-8761-49A3-A313-E7834B16687D}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q1" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{FCD520AB-D938-4542-9B56-AEC07AB5F1DC}" name="Year of Delivery-LAS - Q1" dataDxfId="51"/>
-    <tableColumn id="7" xr3:uid="{674474DE-9D20-41C1-8261-DA9C4A95671C}" name="SOURCE - LAS (CO,RO, SDO) - Q1" dataDxfId="50"/>
-    <tableColumn id="8" xr3:uid="{58D9CB98-8F6F-4F61-9103-C27B8FFBDB51}" name="GAP - LAS - Q1" dataDxfId="49">
+    <tableColumn id="5" xr3:uid="{9CE2D7B1-8761-49A3-A313-E7834B16687D}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q1" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{FCD520AB-D938-4542-9B56-AEC07AB5F1DC}" name="Year of Delivery-LAS - Q1" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{674474DE-9D20-41C1-8261-DA9C4A95671C}" name="SOURCE - LAS (CO,RO, SDO) - Q1" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{58D9CB98-8F6F-4F61-9103-C27B8FFBDB51}" name="GAP - LAS - Q1" dataDxfId="48">
       <calculatedColumnFormula>IF((D3-E3)&lt;0,0,(D3-E3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E6406FC4-4491-4FD6-9EA2-F088E94C44F4}" name="SURPLUS - LAS - Q1" dataDxfId="48">
+    <tableColumn id="9" xr3:uid="{E6406FC4-4491-4FD6-9EA2-F088E94C44F4}" name="SURPLUS - LAS - Q1" dataDxfId="47">
       <calculatedColumnFormula>IF((E3-D3)&lt;0,0,(E3-D3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1E56D889-DC27-4BCB-B61E-06BBBE734949}" name="Quantity based on Target LAS - Q2" dataDxfId="47">
+    <tableColumn id="10" xr3:uid="{1E56D889-DC27-4BCB-B61E-06BBBE734949}" name="Quantity based on Target LAS - Q2" dataDxfId="46">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{E933BF99-834C-4F15-8181-7D005013BD85}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) Q2" dataDxfId="46"/>
-    <tableColumn id="12" xr3:uid="{F2E2CB95-E0BD-4C6E-ACFE-F201177004A0}" name="Year of Delivery-LAS Q2" dataDxfId="45"/>
-    <tableColumn id="13" xr3:uid="{163FBFFB-0AB7-44C8-89C4-72AA64C1EAC7}" name="SOURCE-LAS (CO,RO, SDO) Q2" dataDxfId="44"/>
-    <tableColumn id="14" xr3:uid="{EACC05A8-C68D-4495-BC08-73F093C4992F}" name="GAP - LAS -Q2" dataDxfId="43"/>
-    <tableColumn id="15" xr3:uid="{28A44E24-3E28-4B7F-BADE-28BB84F0B810}" name="SURPLUS - LAS -Q2" dataDxfId="42"/>
-    <tableColumn id="16" xr3:uid="{87878677-5715-46B6-9BA9-9D08DE9A3335}" name="Quantity based on Target LAS - Q3" dataDxfId="41">
+    <tableColumn id="11" xr3:uid="{E933BF99-834C-4F15-8181-7D005013BD85}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) Q2" dataDxfId="45"/>
+    <tableColumn id="12" xr3:uid="{F2E2CB95-E0BD-4C6E-ACFE-F201177004A0}" name="Year of Delivery-LAS Q2" dataDxfId="44"/>
+    <tableColumn id="13" xr3:uid="{163FBFFB-0AB7-44C8-89C4-72AA64C1EAC7}" name="SOURCE-LAS (CO,RO, SDO) Q2" dataDxfId="43"/>
+    <tableColumn id="14" xr3:uid="{EACC05A8-C68D-4495-BC08-73F093C4992F}" name="GAP - LAS -Q2" dataDxfId="42"/>
+    <tableColumn id="15" xr3:uid="{28A44E24-3E28-4B7F-BADE-28BB84F0B810}" name="SURPLUS - LAS -Q2" dataDxfId="41"/>
+    <tableColumn id="16" xr3:uid="{87878677-5715-46B6-9BA9-9D08DE9A3335}" name="Quantity based on Target LAS - Q3" dataDxfId="40">
       <calculatedColumnFormula>#REF!*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{48667A1F-77B1-47A6-83F7-61ED15F61DDB}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q3" dataDxfId="40"/>
-    <tableColumn id="18" xr3:uid="{56F2625D-2CEE-478E-A8DE-42A7191C3835}" name="Year of Delivery-LAS - Q3" dataDxfId="39"/>
-    <tableColumn id="19" xr3:uid="{EF0F614F-5FED-4639-8798-840D9677B8DA}" name="SOURCE-LAS (CO,RO, SDO) - Q3" dataDxfId="38"/>
-    <tableColumn id="20" xr3:uid="{FD91DDEE-DBA8-4E2C-94B2-23AE9F73CC4A}" name="GAP - LAS - Q3" dataDxfId="37">
+    <tableColumn id="17" xr3:uid="{48667A1F-77B1-47A6-83F7-61ED15F61DDB}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q3" dataDxfId="39"/>
+    <tableColumn id="18" xr3:uid="{56F2625D-2CEE-478E-A8DE-42A7191C3835}" name="Year of Delivery-LAS - Q3" dataDxfId="38"/>
+    <tableColumn id="19" xr3:uid="{EF0F614F-5FED-4639-8798-840D9677B8DA}" name="SOURCE-LAS (CO,RO, SDO) - Q3" dataDxfId="37"/>
+    <tableColumn id="20" xr3:uid="{FD91DDEE-DBA8-4E2C-94B2-23AE9F73CC4A}" name="GAP - LAS - Q3" dataDxfId="36">
       <calculatedColumnFormula>IF((P3-Q3)&lt;0,0,(P3-Q3))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="21" xr3:uid="{DB598C6C-E489-4B0F-9BC6-B0981F7D2582}" name="SURPLUS - LAS - Q3" dataDxfId="36">
-      <calculatedColumnFormula>IF((Q3-P3)&lt;0,0,(Q3-P3))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="22" xr3:uid="{8CD6906A-7980-46E8-80B2-8563AEBC71F7}" name="Quantity based on Target LAS - Q4" dataDxfId="35">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
@@ -3119,10 +3048,10 @@
     <tableColumn id="24" xr3:uid="{205BCDBA-0424-492C-B4EF-841B8A3A1521}" name="Year of Delivery - LAS - Q4" dataDxfId="33"/>
     <tableColumn id="25" xr3:uid="{8226E35B-1F3B-4D2A-815B-9D4C0A24EE7E}" name="SOURCE - LAS (CO,RO, SDO) - Q4" dataDxfId="32"/>
     <tableColumn id="26" xr3:uid="{5B37A4B7-CD16-4D9A-8A47-D9EA73F613BC}" name="GAP - LAS - Q4" dataDxfId="31">
-      <calculatedColumnFormula>IF((V3-W3)&lt;0,0,(V3-W3))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF((U3-V3)&lt;0,0,(U3-V3))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="27" xr3:uid="{38E9C5F3-3FF5-4B13-A9DA-0081A90F35C5}" name="SURPLUS - LAS - Q4" dataDxfId="30">
-      <calculatedColumnFormula>IF((W3-V3)&lt;0,0,(W3-V3))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF((V3-U3)&lt;0,0,(V3-U3))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3511,11 +3440,6 @@
     <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.140625" customWidth="1"/>
     <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" customWidth="1"/>
-    <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="15" width="11.85546875" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
@@ -3545,24 +3469,12 @@
       </c>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
-      <c r="K1" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="N1" s="44" t="s">
-        <v>5</v>
-      </c>
-      <c r="O1" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" s="46" t="s">
-        <v>7</v>
-      </c>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
       <c r="S1" s="6"/>
@@ -3605,12 +3517,6 @@
         <f>IF((D2-C2)&lt;0,0,D2-C2)</f>
         <v>203</v>
       </c>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
     </row>
     <row r="3" spans="1:30" ht="29.25" customHeight="1">
       <c r="A3" s="1">
@@ -3639,12 +3545,6 @@
         <f>IF((D3-C3)&lt;0,0,D3-C3)</f>
         <v>203</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
-      <c r="P3" s="42"/>
     </row>
     <row r="4" spans="1:30" ht="21" customHeight="1">
       <c r="A4" s="1">
@@ -3673,12 +3573,6 @@
         <f>IF((D4-C4)&lt;0,0,D4-C4)</f>
         <v>203</v>
       </c>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="42"/>
     </row>
     <row r="5" spans="1:30" ht="25.5" customHeight="1">
       <c r="A5" s="1">
@@ -3707,12 +3601,6 @@
         <f t="shared" ref="H5:H6" si="1">IF((D5-C5)&lt;0,0,D5-C5)</f>
         <v>203</v>
       </c>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="42"/>
     </row>
     <row r="6" spans="1:30" ht="19.5">
       <c r="A6" s="1">
@@ -3737,23 +3625,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
     </row>
     <row r="7" spans="1:30">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="42"/>
     </row>
     <row r="8" spans="1:30" ht="39.75" customHeight="1">
       <c r="A8" s="1">
@@ -3778,12 +3654,6 @@
         <f>IF((D8-C8)&lt;0,0,D8-C8)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
-      <c r="N8" s="42"/>
-      <c r="O8" s="42"/>
-      <c r="P8" s="42"/>
     </row>
     <row r="9" spans="1:30" ht="29.25" customHeight="1">
       <c r="A9" s="1">
@@ -3808,12 +3678,6 @@
         <f>IF((D9-C9)&lt;0,0,D9-C9)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42"/>
-      <c r="N9" s="42"/>
-      <c r="O9" s="42"/>
-      <c r="P9" s="42"/>
     </row>
     <row r="10" spans="1:30" ht="28.5" customHeight="1">
       <c r="A10" s="1">
@@ -3837,12 +3701,6 @@
       <c r="H10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="42"/>
-      <c r="P10" s="42"/>
     </row>
     <row r="11" spans="1:30" ht="24" customHeight="1">
       <c r="A11" s="1">
@@ -3867,12 +3725,6 @@
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="42"/>
-      <c r="P11" s="42"/>
     </row>
     <row r="12" spans="1:30" ht="19.5">
       <c r="A12" s="1">
@@ -3897,23 +3749,11 @@
         <f>IF((D12-C12)&lt;0,0,D12-C12)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="42"/>
-      <c r="L12" s="42"/>
-      <c r="M12" s="42"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="42"/>
-      <c r="P12" s="42"/>
     </row>
     <row r="13" spans="1:30">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
-      <c r="K13" s="42"/>
-      <c r="L13" s="42"/>
-      <c r="M13" s="42"/>
-      <c r="N13" s="42"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="42"/>
     </row>
     <row r="14" spans="1:30" ht="49.5" customHeight="1">
       <c r="A14" s="1">
@@ -3938,12 +3778,6 @@
         <f t="shared" ref="H14:H19" si="3">IF((D14-C14)&lt;0,0,D14-C14)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="42"/>
-      <c r="L14" s="42"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="42"/>
-      <c r="O14" s="42"/>
-      <c r="P14" s="42"/>
     </row>
     <row r="15" spans="1:30" ht="29.25" customHeight="1">
       <c r="A15" s="1">
@@ -3968,12 +3802,6 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K15" s="42"/>
-      <c r="L15" s="42"/>
-      <c r="M15" s="42"/>
-      <c r="N15" s="42"/>
-      <c r="O15" s="42"/>
-      <c r="P15" s="42"/>
     </row>
     <row r="16" spans="1:30" ht="27" customHeight="1">
       <c r="A16" s="1">
@@ -3998,14 +3826,8 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K16" s="42"/>
-      <c r="L16" s="42"/>
-      <c r="M16" s="42"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="42"/>
-      <c r="P16" s="42"/>
-    </row>
-    <row r="17" spans="1:16" ht="23.25" customHeight="1">
+    </row>
+    <row r="17" spans="1:8" ht="23.25" customHeight="1">
       <c r="A17" s="1">
         <v>3</v>
       </c>
@@ -4028,14 +3850,8 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="42"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="42"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="42"/>
-      <c r="P17" s="42"/>
-    </row>
-    <row r="18" spans="1:16" ht="21" customHeight="1">
+    </row>
+    <row r="18" spans="1:8" ht="21" customHeight="1">
       <c r="A18" s="1">
         <v>3</v>
       </c>
@@ -4058,14 +3874,8 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="42"/>
-    </row>
-    <row r="19" spans="1:16" ht="19.5">
+    </row>
+    <row r="19" spans="1:8" ht="19.5">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -4088,14 +3898,8 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="42"/>
-    </row>
-    <row r="20" spans="1:16">
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -4104,14 +3908,8 @@
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="42"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="42"/>
-      <c r="O20" s="42"/>
-      <c r="P20" s="42"/>
-    </row>
-    <row r="21" spans="1:16" ht="28.5" customHeight="1">
+    </row>
+    <row r="21" spans="1:8" ht="28.5" customHeight="1">
       <c r="A21" s="1">
         <v>4</v>
       </c>
@@ -4134,14 +3932,8 @@
         <f t="shared" ref="H21:H29" si="5">IF((D21-C21)&lt;0,0,D21-C21)</f>
         <v>0</v>
       </c>
-      <c r="K21" s="42"/>
-      <c r="L21" s="42"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="42"/>
-      <c r="O21" s="42"/>
-      <c r="P21" s="42"/>
-    </row>
-    <row r="22" spans="1:16" ht="24" customHeight="1">
+    </row>
+    <row r="22" spans="1:8" ht="24" customHeight="1">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -4168,14 +3960,8 @@
         <f t="shared" si="5"/>
         <v>201</v>
       </c>
-      <c r="K22" s="42"/>
-      <c r="L22" s="42"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="42"/>
-      <c r="O22" s="42"/>
-      <c r="P22" s="42"/>
-    </row>
-    <row r="23" spans="1:16" ht="19.5">
+    </row>
+    <row r="23" spans="1:8" ht="19.5">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -4202,14 +3988,8 @@
         <f t="shared" si="5"/>
         <v>201</v>
       </c>
-      <c r="K23" s="42"/>
-      <c r="L23" s="42"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="42"/>
-      <c r="O23" s="42"/>
-      <c r="P23" s="42"/>
-    </row>
-    <row r="24" spans="1:16" ht="27" customHeight="1">
+    </row>
+    <row r="24" spans="1:8" ht="27" customHeight="1">
       <c r="A24" s="1">
         <v>4</v>
       </c>
@@ -4236,14 +4016,8 @@
         <f t="shared" si="5"/>
         <v>201</v>
       </c>
-      <c r="K24" s="42"/>
-      <c r="L24" s="42"/>
-      <c r="M24" s="42"/>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-    </row>
-    <row r="25" spans="1:16" ht="33.75" customHeight="1">
+    </row>
+    <row r="25" spans="1:8" ht="33.75" customHeight="1">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -4270,14 +4044,8 @@
         <f t="shared" si="5"/>
         <v>201</v>
       </c>
-      <c r="K25" s="42"/>
-      <c r="L25" s="42"/>
-      <c r="M25" s="42"/>
-      <c r="N25" s="42"/>
-      <c r="O25" s="42"/>
-      <c r="P25" s="42"/>
-    </row>
-    <row r="26" spans="1:16" ht="33.75" customHeight="1">
+    </row>
+    <row r="26" spans="1:8" ht="33.75" customHeight="1">
       <c r="A26" s="1">
         <v>4</v>
       </c>
@@ -4304,14 +4072,8 @@
         <f t="shared" si="5"/>
         <v>201</v>
       </c>
-      <c r="K26" s="42"/>
-      <c r="L26" s="42"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="42"/>
-      <c r="P26" s="42"/>
-    </row>
-    <row r="27" spans="1:16" ht="33.75" customHeight="1">
+    </row>
+    <row r="27" spans="1:8" ht="33.75" customHeight="1">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -4338,14 +4100,8 @@
         <f t="shared" si="5"/>
         <v>201</v>
       </c>
-      <c r="K27" s="42"/>
-      <c r="L27" s="42"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="42"/>
-      <c r="O27" s="42"/>
-      <c r="P27" s="42"/>
-    </row>
-    <row r="28" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="28" spans="1:8" ht="27.75" customHeight="1">
       <c r="A28" s="1">
         <v>4</v>
       </c>
@@ -4368,14 +4124,8 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K28" s="42"/>
-      <c r="L28" s="42"/>
-      <c r="M28" s="42"/>
-      <c r="N28" s="42"/>
-      <c r="O28" s="42"/>
-      <c r="P28" s="42"/>
-    </row>
-    <row r="29" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="29" spans="1:8" ht="27.75" customHeight="1">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -4398,14 +4148,8 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K29" s="42"/>
-      <c r="L29" s="42"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="42"/>
-      <c r="O29" s="42"/>
-      <c r="P29" s="42"/>
-    </row>
-    <row r="30" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="30" spans="1:8" ht="27.75" customHeight="1">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -4414,14 +4158,8 @@
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
-      <c r="K30" s="42"/>
-      <c r="L30" s="42"/>
-      <c r="M30" s="42"/>
-      <c r="N30" s="42"/>
-      <c r="O30" s="42"/>
-      <c r="P30" s="42"/>
-    </row>
-    <row r="31" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="31" spans="1:8" ht="27.75" customHeight="1">
       <c r="A31" s="1">
         <v>5</v>
       </c>
@@ -4448,14 +4186,8 @@
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
         <v>88</v>
       </c>
-      <c r="K31" s="42"/>
-      <c r="L31" s="42"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="42"/>
-      <c r="O31" s="42"/>
-      <c r="P31" s="42"/>
-    </row>
-    <row r="32" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="32" spans="1:8" ht="27.75" customHeight="1">
       <c r="A32" s="1">
         <v>5</v>
       </c>
@@ -4478,14 +4210,8 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K32" s="42"/>
-      <c r="L32" s="42"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="42"/>
-      <c r="O32" s="42"/>
-      <c r="P32" s="42"/>
-    </row>
-    <row r="33" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="33" spans="1:8" ht="27.75" customHeight="1">
       <c r="A33" s="1">
         <v>5</v>
       </c>
@@ -4508,14 +4234,8 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K33" s="42"/>
-      <c r="L33" s="42"/>
-      <c r="M33" s="42"/>
-      <c r="N33" s="42"/>
-      <c r="O33" s="42"/>
-      <c r="P33" s="42"/>
-    </row>
-    <row r="34" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="34" spans="1:8" ht="27.75" customHeight="1">
       <c r="A34" s="1">
         <v>5</v>
       </c>
@@ -4538,14 +4258,8 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K34" s="42"/>
-      <c r="L34" s="42"/>
-      <c r="M34" s="42"/>
-      <c r="N34" s="42"/>
-      <c r="O34" s="42"/>
-      <c r="P34" s="42"/>
-    </row>
-    <row r="35" spans="1:16" ht="39" customHeight="1">
+    </row>
+    <row r="35" spans="1:8" ht="39" customHeight="1">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -4572,14 +4286,8 @@
         <f t="shared" si="7"/>
         <v>88</v>
       </c>
-      <c r="K35" s="42"/>
-      <c r="L35" s="42"/>
-      <c r="M35" s="42"/>
-      <c r="N35" s="42"/>
-      <c r="O35" s="42"/>
-      <c r="P35" s="42"/>
-    </row>
-    <row r="36" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="36" spans="1:8" ht="27.75" customHeight="1">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -4606,14 +4314,8 @@
         <f t="shared" si="7"/>
         <v>88</v>
       </c>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-    </row>
-    <row r="37" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="37" spans="1:8" ht="27.75" customHeight="1">
       <c r="A37" s="1">
         <v>5</v>
       </c>
@@ -4640,14 +4342,8 @@
         <f t="shared" si="7"/>
         <v>88</v>
       </c>
-      <c r="K37" s="42"/>
-      <c r="L37" s="42"/>
-      <c r="M37" s="42"/>
-      <c r="N37" s="42"/>
-      <c r="O37" s="42"/>
-      <c r="P37" s="42"/>
-    </row>
-    <row r="38" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="38" spans="1:8" ht="27.75" customHeight="1">
       <c r="A38" s="1">
         <v>5</v>
       </c>
@@ -4670,14 +4366,8 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K38" s="42"/>
-      <c r="L38" s="42"/>
-      <c r="M38" s="42"/>
-      <c r="N38" s="42"/>
-      <c r="O38" s="42"/>
-      <c r="P38" s="42"/>
-    </row>
-    <row r="39" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="39" spans="1:8" ht="27.75" customHeight="1">
       <c r="A39" s="1">
         <v>5</v>
       </c>
@@ -4700,14 +4390,8 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K39" s="42"/>
-      <c r="L39" s="42"/>
-      <c r="M39" s="42"/>
-      <c r="N39" s="42"/>
-      <c r="O39" s="42"/>
-      <c r="P39" s="42"/>
-    </row>
-    <row r="40" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="40" spans="1:8" ht="27.75" customHeight="1">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -4716,14 +4400,8 @@
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
-      <c r="K40" s="42"/>
-      <c r="L40" s="42"/>
-      <c r="M40" s="42"/>
-      <c r="N40" s="42"/>
-      <c r="O40" s="42"/>
-      <c r="P40" s="42"/>
-    </row>
-    <row r="41" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="41" spans="1:8" ht="27.75" customHeight="1">
       <c r="A41" s="1">
         <v>6</v>
       </c>
@@ -4746,14 +4424,8 @@
         <f t="shared" ref="H41:H49" si="9">IF((D41-C41)&lt;0,0,D41-C41)</f>
         <v>0</v>
       </c>
-      <c r="K41" s="42"/>
-      <c r="L41" s="42"/>
-      <c r="M41" s="42"/>
-      <c r="N41" s="42"/>
-      <c r="O41" s="42"/>
-      <c r="P41" s="42"/>
-    </row>
-    <row r="42" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="42" spans="1:8" ht="27.75" customHeight="1">
       <c r="A42" s="1">
         <v>6</v>
       </c>
@@ -4776,14 +4448,8 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-    </row>
-    <row r="43" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="43" spans="1:8" ht="27.75" customHeight="1">
       <c r="A43" s="1">
         <v>6</v>
       </c>
@@ -4806,14 +4472,8 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="K43" s="42"/>
-      <c r="L43" s="42"/>
-      <c r="M43" s="42"/>
-      <c r="N43" s="42"/>
-      <c r="O43" s="42"/>
-      <c r="P43" s="42"/>
-    </row>
-    <row r="44" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="44" spans="1:8" ht="27.75" customHeight="1">
       <c r="A44" s="1">
         <v>6</v>
       </c>
@@ -4836,14 +4496,8 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="K44" s="42"/>
-      <c r="L44" s="42"/>
-      <c r="M44" s="42"/>
-      <c r="N44" s="42"/>
-      <c r="O44" s="42"/>
-      <c r="P44" s="42"/>
-    </row>
-    <row r="45" spans="1:16" ht="36.75" customHeight="1">
+    </row>
+    <row r="45" spans="1:8" ht="36.75" customHeight="1">
       <c r="A45" s="1">
         <v>6</v>
       </c>
@@ -4866,14 +4520,8 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="K45" s="42"/>
-      <c r="L45" s="42"/>
-      <c r="M45" s="42"/>
-      <c r="N45" s="42"/>
-      <c r="O45" s="42"/>
-      <c r="P45" s="42"/>
-    </row>
-    <row r="46" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="46" spans="1:8" ht="27.75" customHeight="1">
       <c r="A46" s="1">
         <v>6</v>
       </c>
@@ -4896,14 +4544,8 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="K46" s="42"/>
-      <c r="L46" s="42"/>
-      <c r="M46" s="42"/>
-      <c r="N46" s="42"/>
-      <c r="O46" s="42"/>
-      <c r="P46" s="42"/>
-    </row>
-    <row r="47" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="47" spans="1:8" ht="27.75" customHeight="1">
       <c r="A47" s="1">
         <v>6</v>
       </c>
@@ -4926,14 +4568,8 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="K47" s="42"/>
-      <c r="L47" s="42"/>
-      <c r="M47" s="42"/>
-      <c r="N47" s="42"/>
-      <c r="O47" s="42"/>
-      <c r="P47" s="42"/>
-    </row>
-    <row r="48" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="48" spans="1:8" ht="27.75" customHeight="1">
       <c r="A48" s="1">
         <v>6</v>
       </c>
@@ -4956,14 +4592,8 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="K48" s="42"/>
-      <c r="L48" s="42"/>
-      <c r="M48" s="42"/>
-      <c r="N48" s="42"/>
-      <c r="O48" s="42"/>
-      <c r="P48" s="42"/>
-    </row>
-    <row r="49" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="49" spans="1:8" ht="27.75" customHeight="1">
       <c r="A49" s="1">
         <v>6</v>
       </c>
@@ -4986,14 +4616,8 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="K49" s="42"/>
-      <c r="L49" s="42"/>
-      <c r="M49" s="42"/>
-      <c r="N49" s="42"/>
-      <c r="O49" s="42"/>
-      <c r="P49" s="42"/>
-    </row>
-    <row r="50" spans="1:16" ht="27.75" customHeight="1">
+    </row>
+    <row r="50" spans="1:8" ht="27.75" customHeight="1">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
@@ -5003,7 +4627,7 @@
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:16" ht="27.75" customHeight="1">
+    <row r="51" spans="1:8" ht="27.75" customHeight="1">
       <c r="A51" s="10">
         <v>7</v>
       </c>
@@ -5023,7 +4647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="27.75" customHeight="1">
+    <row r="52" spans="1:8" ht="27.75" customHeight="1">
       <c r="A52" s="10">
         <v>7</v>
       </c>
@@ -5043,7 +4667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="27.75" customHeight="1">
+    <row r="53" spans="1:8" ht="27.75" customHeight="1">
       <c r="A53" s="10">
         <v>7</v>
       </c>
@@ -5063,7 +4687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="27.75" customHeight="1">
+    <row r="54" spans="1:8" ht="27.75" customHeight="1">
       <c r="A54" s="10">
         <v>7</v>
       </c>
@@ -5083,7 +4707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="39" customHeight="1">
+    <row r="55" spans="1:8" ht="39" customHeight="1">
       <c r="A55" s="10">
         <v>7</v>
       </c>
@@ -5103,7 +4727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="27.75" customHeight="1">
+    <row r="56" spans="1:8" ht="27.75" customHeight="1">
       <c r="A56" s="10">
         <v>7</v>
       </c>
@@ -5123,7 +4747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="27.75" customHeight="1">
+    <row r="57" spans="1:8" ht="27.75" customHeight="1">
       <c r="A57" s="10">
         <v>7</v>
       </c>
@@ -5143,7 +4767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="27.75" customHeight="1">
+    <row r="58" spans="1:8" ht="27.75" customHeight="1">
       <c r="A58" s="10">
         <v>7</v>
       </c>
@@ -5163,7 +4787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="27.75" customHeight="1">
+    <row r="59" spans="1:8" ht="27.75" customHeight="1">
       <c r="A59" s="10">
         <v>7</v>
       </c>
@@ -5183,7 +4807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="27.75" customHeight="1">
+    <row r="60" spans="1:8" ht="27.75" customHeight="1">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -5193,7 +4817,7 @@
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:16" ht="27.75" customHeight="1">
+    <row r="61" spans="1:8" ht="27.75" customHeight="1">
       <c r="A61" s="10">
         <v>8</v>
       </c>
@@ -5213,7 +4837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="27.75" customHeight="1">
+    <row r="62" spans="1:8" ht="27.75" customHeight="1">
       <c r="A62" s="10">
         <v>8</v>
       </c>
@@ -5233,7 +4857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:16" ht="27.75" customHeight="1">
+    <row r="63" spans="1:8" ht="27.75" customHeight="1">
       <c r="A63" s="10">
         <v>8</v>
       </c>
@@ -5253,7 +4877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:16" ht="27.75" customHeight="1">
+    <row r="64" spans="1:8" ht="27.75" customHeight="1">
       <c r="A64" s="10">
         <v>8</v>
       </c>
@@ -5927,8 +5551,6 @@
   <protectedRanges>
     <protectedRange sqref="C1:E98" name="Textbooks"/>
     <protectedRange sqref="F1:F98" name="SOURCE"/>
-    <protectedRange sqref="K1:M1" name="Textbooks_1"/>
-    <protectedRange sqref="N1" name="SOURCE_1"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
@@ -5948,7 +5570,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA127"/>
+  <dimension ref="A1:AA135"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5978,38 +5600,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="48" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="49" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="50" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -6072,31 +5694,28 @@
       <c r="T2" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="U2" s="24" t="s">
+      <c r="U2" s="26" t="s">
         <v>56</v>
       </c>
       <c r="V2" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="W2" s="26" t="s">
+      <c r="W2" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="X2" s="41" t="s">
         <v>59</v>
       </c>
       <c r="Y2" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="Z2" s="41" t="s">
+      <c r="Z2" s="26" t="s">
         <v>61</v>
-      </c>
-      <c r="AA2" s="26" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="30.6" customHeight="1">
       <c r="A3" s="39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="32">
@@ -6144,26 +5763,22 @@
         <v>3928</v>
       </c>
       <c r="U3" s="34">
-        <f>IF((Q3-P3)&lt;0,0,(Q3-P3))</f>
-        <v>0</v>
-      </c>
-      <c r="V3" s="34">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3928</v>
       </c>
-      <c r="W3" s="34"/>
-      <c r="X3" s="32"/>
-      <c r="Y3" s="34"/>
+      <c r="V3" s="34"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="34"/>
+      <c r="Y3" s="34">
+        <f>IF((U3-V3)&lt;0,0,(U3-V3))</f>
+        <v>3928</v>
+      </c>
       <c r="Z3" s="34">
-        <f>IF((V3-W3)&lt;0,0,(V3-W3))</f>
-        <v>3928</v>
-      </c>
-      <c r="AA3" s="34">
-        <f>IF((W3-V3)&lt;0,0,(W3-V3))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+        <f>IF((V3-U3)&lt;0,0,(V3-U3))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -6171,9 +5786,8 @@
       <c r="S4" s="5"/>
       <c r="T4" s="13"/>
       <c r="U4" s="13"/>
-      <c r="V4" s="13"/>
+      <c r="Y4" s="13"/>
       <c r="Z4" s="13"/>
-      <c r="AA4" s="13"/>
     </row>
     <row r="5" spans="1:27" ht="38.25">
       <c r="A5" s="1">
@@ -6239,22 +5853,18 @@
         <v>3696</v>
       </c>
       <c r="U5" s="5">
-        <f t="shared" ref="U5" si="7">IF((Q5-P5)&lt;0,0,(Q5-P5))</f>
-        <v>0</v>
-      </c>
-      <c r="V5" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3696</v>
       </c>
-      <c r="W5" s="5"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5">
+        <f t="shared" ref="Y5" si="7">IF((U5-V5)&lt;0,0,(U5-V5))</f>
+        <v>3696</v>
+      </c>
       <c r="Z5" s="5">
-        <f t="shared" ref="Z5" si="8">IF((V5-W5)&lt;0,0,(V5-W5))</f>
-        <v>3696</v>
-      </c>
-      <c r="AA5" s="5">
-        <f t="shared" ref="AA5" si="9">IF((W5-V5)&lt;0,0,(W5-V5))</f>
+        <f t="shared" ref="Z5" si="8">IF((V5-U5)&lt;0,0,(V5-U5))</f>
         <v>0</v>
       </c>
     </row>
@@ -6303,11 +5913,11 @@
         <v>9</v>
       </c>
       <c r="N6" s="5">
-        <f t="shared" ref="N6:N69" si="10">IF((J6-K6)&lt;0,0,(J6-K6))</f>
+        <f t="shared" ref="N6:N69" si="9">IF((J6-K6)&lt;0,0,(J6-K6))</f>
         <v>3251</v>
       </c>
       <c r="O6" s="5">
-        <f t="shared" ref="O6:O69" si="11">IF((K6-J6)&lt;0,0,(K6-J6))</f>
+        <f t="shared" ref="O6:O69" si="10">IF((K6-J6)&lt;0,0,(K6-J6))</f>
         <v>0</v>
       </c>
       <c r="P6" s="5">
@@ -6318,26 +5928,22 @@
       <c r="R6" s="1"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5">
-        <f t="shared" ref="T6:T69" si="12">IF((P6-Q6)&lt;0,0,(P6-Q6))</f>
+        <f t="shared" ref="T6:T69" si="11">IF((P6-Q6)&lt;0,0,(P6-Q6))</f>
         <v>3696</v>
       </c>
       <c r="U6" s="5">
-        <f t="shared" ref="U6:U69" si="13">IF((Q6-P6)&lt;0,0,(Q6-P6))</f>
-        <v>0</v>
-      </c>
-      <c r="V6" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3696</v>
       </c>
-      <c r="W6" s="5"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5">
+        <f t="shared" ref="Y6:Y69" si="12">IF((U6-V6)&lt;0,0,(U6-V6))</f>
+        <v>3696</v>
+      </c>
       <c r="Z6" s="5">
-        <f t="shared" ref="Z6:Z69" si="14">IF((V6-W6)&lt;0,0,(V6-W6))</f>
-        <v>3696</v>
-      </c>
-      <c r="AA6" s="5">
-        <f t="shared" ref="AA6:AA69" si="15">IF((W6-V6)&lt;0,0,(W6-V6))</f>
+        <f t="shared" ref="Z6:Z69" si="13">IF((V6-U6)&lt;0,0,(V6-U6))</f>
         <v>0</v>
       </c>
     </row>
@@ -6386,11 +5992,11 @@
         <v>9</v>
       </c>
       <c r="N7" s="5">
+        <f t="shared" si="9"/>
+        <v>3251</v>
+      </c>
+      <c r="O7" s="5">
         <f t="shared" si="10"/>
-        <v>3251</v>
-      </c>
-      <c r="O7" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P7" s="5">
@@ -6401,26 +6007,22 @@
       <c r="R7" s="1"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5">
+        <f t="shared" si="11"/>
+        <v>3696</v>
+      </c>
+      <c r="U7" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>3696</v>
+      </c>
+      <c r="V7" s="5"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5">
         <f t="shared" si="12"/>
         <v>3696</v>
       </c>
-      <c r="U7" s="5">
+      <c r="Z7" s="5">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V7" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3696</v>
-      </c>
-      <c r="W7" s="5"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="5"/>
-      <c r="Z7" s="5">
-        <f t="shared" si="14"/>
-        <v>3696</v>
-      </c>
-      <c r="AA7" s="5">
-        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -6469,11 +6071,11 @@
         <v>9</v>
       </c>
       <c r="N8" s="5">
+        <f t="shared" si="9"/>
+        <v>3251</v>
+      </c>
+      <c r="O8" s="5">
         <f t="shared" si="10"/>
-        <v>3251</v>
-      </c>
-      <c r="O8" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P8" s="5">
@@ -6484,26 +6086,22 @@
       <c r="R8" s="1"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5">
+        <f t="shared" si="11"/>
+        <v>3696</v>
+      </c>
+      <c r="U8" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>3696</v>
+      </c>
+      <c r="V8" s="5"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5">
         <f t="shared" si="12"/>
         <v>3696</v>
       </c>
-      <c r="U8" s="5">
+      <c r="Z8" s="5">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V8" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3696</v>
-      </c>
-      <c r="W8" s="5"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="5"/>
-      <c r="Z8" s="5">
-        <f t="shared" si="14"/>
-        <v>3696</v>
-      </c>
-      <c r="AA8" s="5">
-        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -6552,11 +6150,11 @@
         <v>9</v>
       </c>
       <c r="N9" s="5">
+        <f t="shared" si="9"/>
+        <v>3251</v>
+      </c>
+      <c r="O9" s="5">
         <f t="shared" si="10"/>
-        <v>3251</v>
-      </c>
-      <c r="O9" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P9" s="5">
@@ -6567,26 +6165,22 @@
       <c r="R9" s="1"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
+        <f t="shared" si="11"/>
+        <v>3696</v>
+      </c>
+      <c r="U9" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>3696</v>
+      </c>
+      <c r="V9" s="5"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5">
         <f t="shared" si="12"/>
         <v>3696</v>
       </c>
-      <c r="U9" s="5">
+      <c r="Z9" s="5">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V9" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3696</v>
-      </c>
-      <c r="W9" s="5"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="5"/>
-      <c r="Z9" s="5">
-        <f t="shared" si="14"/>
-        <v>3696</v>
-      </c>
-      <c r="AA9" s="5">
-        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -6635,11 +6229,11 @@
         <v>9</v>
       </c>
       <c r="N10" s="5">
+        <f t="shared" si="9"/>
+        <v>3251</v>
+      </c>
+      <c r="O10" s="5">
         <f t="shared" si="10"/>
-        <v>3251</v>
-      </c>
-      <c r="O10" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P10" s="5">
@@ -6650,26 +6244,22 @@
       <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
+        <f t="shared" si="11"/>
+        <v>3696</v>
+      </c>
+      <c r="U10" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>3696</v>
+      </c>
+      <c r="V10" s="5"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5">
         <f t="shared" si="12"/>
         <v>3696</v>
       </c>
-      <c r="U10" s="5">
+      <c r="Z10" s="5">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V10" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3696</v>
-      </c>
-      <c r="W10" s="5"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="5"/>
-      <c r="Z10" s="5">
-        <f t="shared" si="14"/>
-        <v>3696</v>
-      </c>
-      <c r="AA10" s="5">
-        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -6718,11 +6308,11 @@
         <v>9</v>
       </c>
       <c r="N11" s="5">
+        <f t="shared" si="9"/>
+        <v>3251</v>
+      </c>
+      <c r="O11" s="5">
         <f t="shared" si="10"/>
-        <v>3251</v>
-      </c>
-      <c r="O11" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P11" s="5">
@@ -6733,26 +6323,22 @@
       <c r="R11" s="1"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5">
+        <f t="shared" si="11"/>
+        <v>3696</v>
+      </c>
+      <c r="U11" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>3696</v>
+      </c>
+      <c r="V11" s="5"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5">
         <f t="shared" si="12"/>
         <v>3696</v>
       </c>
-      <c r="U11" s="5">
+      <c r="Z11" s="5">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V11" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3696</v>
-      </c>
-      <c r="W11" s="5"/>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="5"/>
-      <c r="Z11" s="5">
-        <f t="shared" si="14"/>
-        <v>3696</v>
-      </c>
-      <c r="AA11" s="5">
-        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -6761,7 +6347,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12" s="1">
         <v>462</v>
@@ -6801,11 +6387,11 @@
         <v>9</v>
       </c>
       <c r="N12" s="5">
+        <f t="shared" si="9"/>
+        <v>3251</v>
+      </c>
+      <c r="O12" s="5">
         <f t="shared" si="10"/>
-        <v>3251</v>
-      </c>
-      <c r="O12" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P12" s="5">
@@ -6816,30 +6402,26 @@
       <c r="R12" s="1"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5">
+        <f t="shared" si="11"/>
+        <v>3696</v>
+      </c>
+      <c r="U12" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>3696</v>
+      </c>
+      <c r="V12" s="5"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5">
         <f t="shared" si="12"/>
         <v>3696</v>
       </c>
-      <c r="U12" s="5">
+      <c r="Z12" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V12" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3696</v>
-      </c>
-      <c r="W12" s="5"/>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="5">
-        <f t="shared" si="14"/>
-        <v>3696</v>
-      </c>
-      <c r="AA12" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    </row>
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6847,10 +6429,9 @@
       <c r="S13" s="5"/>
       <c r="T13" s="13"/>
       <c r="U13" s="13"/>
-      <c r="V13" s="13"/>
+      <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
       <c r="Z13" s="13"/>
-      <c r="AA13" s="13"/>
     </row>
     <row r="14" spans="1:27" ht="38.25">
       <c r="A14" s="1">
@@ -6897,11 +6478,11 @@
         <v>9</v>
       </c>
       <c r="N14" s="5">
+        <f t="shared" si="9"/>
+        <v>3528</v>
+      </c>
+      <c r="O14" s="5">
         <f t="shared" si="10"/>
-        <v>3528</v>
-      </c>
-      <c r="O14" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P14" s="5">
@@ -6912,26 +6493,22 @@
       <c r="R14" s="1"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5">
+        <f t="shared" si="11"/>
+        <v>4032</v>
+      </c>
+      <c r="U14" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4032</v>
+      </c>
+      <c r="V14" s="5"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5">
         <f t="shared" si="12"/>
         <v>4032</v>
       </c>
-      <c r="U14" s="5">
+      <c r="Z14" s="5">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4032</v>
-      </c>
-      <c r="W14" s="5"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="5"/>
-      <c r="Z14" s="5">
-        <f t="shared" si="14"/>
-        <v>4032</v>
-      </c>
-      <c r="AA14" s="5">
-        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -6980,11 +6557,11 @@
         <v>9</v>
       </c>
       <c r="N15" s="5">
+        <f t="shared" si="9"/>
+        <v>3528</v>
+      </c>
+      <c r="O15" s="5">
         <f t="shared" si="10"/>
-        <v>3528</v>
-      </c>
-      <c r="O15" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P15" s="5">
@@ -6995,26 +6572,22 @@
       <c r="R15" s="1"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5">
+        <f t="shared" si="11"/>
+        <v>4032</v>
+      </c>
+      <c r="U15" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4032</v>
+      </c>
+      <c r="V15" s="5"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5">
         <f t="shared" si="12"/>
         <v>4032</v>
       </c>
-      <c r="U15" s="5">
+      <c r="Z15" s="5">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4032</v>
-      </c>
-      <c r="W15" s="5"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="5"/>
-      <c r="Z15" s="5">
-        <f t="shared" si="14"/>
-        <v>4032</v>
-      </c>
-      <c r="AA15" s="5">
-        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -7063,11 +6636,11 @@
         <v>9</v>
       </c>
       <c r="N16" s="5">
+        <f t="shared" si="9"/>
+        <v>3528</v>
+      </c>
+      <c r="O16" s="5">
         <f t="shared" si="10"/>
-        <v>3528</v>
-      </c>
-      <c r="O16" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P16" s="5">
@@ -7078,30 +6651,26 @@
       <c r="R16" s="1"/>
       <c r="S16" s="5"/>
       <c r="T16" s="5">
+        <f t="shared" si="11"/>
+        <v>4032</v>
+      </c>
+      <c r="U16" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4032</v>
+      </c>
+      <c r="V16" s="5"/>
+      <c r="W16" s="1"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5">
         <f t="shared" si="12"/>
         <v>4032</v>
       </c>
-      <c r="U16" s="5">
+      <c r="Z16" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V16" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4032</v>
-      </c>
-      <c r="W16" s="5"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="5"/>
-      <c r="Z16" s="5">
-        <f t="shared" si="14"/>
-        <v>4032</v>
-      </c>
-      <c r="AA16" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="19.5">
+    </row>
+    <row r="17" spans="1:26" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -7146,11 +6715,11 @@
         <v>9</v>
       </c>
       <c r="N17" s="5">
+        <f t="shared" si="9"/>
+        <v>3528</v>
+      </c>
+      <c r="O17" s="5">
         <f t="shared" si="10"/>
-        <v>3528</v>
-      </c>
-      <c r="O17" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P17" s="5">
@@ -7161,30 +6730,26 @@
       <c r="R17" s="1"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
+        <f t="shared" si="11"/>
+        <v>4032</v>
+      </c>
+      <c r="U17" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4032</v>
+      </c>
+      <c r="V17" s="5"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="5"/>
+      <c r="Y17" s="5">
         <f t="shared" si="12"/>
         <v>4032</v>
       </c>
-      <c r="U17" s="5">
+      <c r="Z17" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V17" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4032</v>
-      </c>
-      <c r="W17" s="5"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="5"/>
-      <c r="Z17" s="5">
-        <f t="shared" si="14"/>
-        <v>4032</v>
-      </c>
-      <c r="AA17" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="19.5">
+    </row>
+    <row r="18" spans="1:26" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -7229,11 +6794,11 @@
         <v>9</v>
       </c>
       <c r="N18" s="5">
+        <f t="shared" si="9"/>
+        <v>3528</v>
+      </c>
+      <c r="O18" s="5">
         <f t="shared" si="10"/>
-        <v>3528</v>
-      </c>
-      <c r="O18" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P18" s="5">
@@ -7244,30 +6809,26 @@
       <c r="R18" s="1"/>
       <c r="S18" s="5"/>
       <c r="T18" s="5">
+        <f t="shared" si="11"/>
+        <v>4032</v>
+      </c>
+      <c r="U18" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4032</v>
+      </c>
+      <c r="V18" s="5"/>
+      <c r="W18" s="1"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5">
         <f t="shared" si="12"/>
         <v>4032</v>
       </c>
-      <c r="U18" s="5">
+      <c r="Z18" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V18" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4032</v>
-      </c>
-      <c r="W18" s="5"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="5"/>
-      <c r="Z18" s="5">
-        <f t="shared" si="14"/>
-        <v>4032</v>
-      </c>
-      <c r="AA18" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="19.5">
+    </row>
+    <row r="19" spans="1:26" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -7312,11 +6873,11 @@
         <v>9</v>
       </c>
       <c r="N19" s="5">
+        <f t="shared" si="9"/>
+        <v>3528</v>
+      </c>
+      <c r="O19" s="5">
         <f t="shared" si="10"/>
-        <v>3528</v>
-      </c>
-      <c r="O19" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P19" s="5">
@@ -7327,30 +6888,26 @@
       <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
+        <f t="shared" si="11"/>
+        <v>4032</v>
+      </c>
+      <c r="U19" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4032</v>
+      </c>
+      <c r="V19" s="5"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5">
         <f t="shared" si="12"/>
         <v>4032</v>
       </c>
-      <c r="U19" s="5">
+      <c r="Z19" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V19" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4032</v>
-      </c>
-      <c r="W19" s="5"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="5"/>
-      <c r="Z19" s="5">
-        <f t="shared" si="14"/>
-        <v>4032</v>
-      </c>
-      <c r="AA19" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="19.5">
+    </row>
+    <row r="20" spans="1:26" ht="19.5">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -7395,11 +6952,11 @@
         <v>9</v>
       </c>
       <c r="N20" s="5">
+        <f t="shared" si="9"/>
+        <v>3528</v>
+      </c>
+      <c r="O20" s="5">
         <f t="shared" si="10"/>
-        <v>3528</v>
-      </c>
-      <c r="O20" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P20" s="5">
@@ -7410,35 +6967,31 @@
       <c r="R20" s="1"/>
       <c r="S20" s="5"/>
       <c r="T20" s="5">
+        <f t="shared" si="11"/>
+        <v>4032</v>
+      </c>
+      <c r="U20" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4032</v>
+      </c>
+      <c r="V20" s="5"/>
+      <c r="W20" s="1"/>
+      <c r="X20" s="5"/>
+      <c r="Y20" s="5">
         <f t="shared" si="12"/>
         <v>4032</v>
       </c>
-      <c r="U20" s="5">
+      <c r="Z20" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V20" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4032</v>
-      </c>
-      <c r="W20" s="5"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="5"/>
-      <c r="Z20" s="5">
-        <f t="shared" si="14"/>
-        <v>4032</v>
-      </c>
-      <c r="AA20" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="19.5">
+    </row>
+    <row r="21" spans="1:26" ht="19.5">
       <c r="A21" s="1">
         <v>2</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21" s="1">
         <v>504</v>
@@ -7478,11 +7031,11 @@
         <v>9</v>
       </c>
       <c r="N21" s="5">
+        <f t="shared" si="9"/>
+        <v>3528</v>
+      </c>
+      <c r="O21" s="5">
         <f t="shared" si="10"/>
-        <v>3528</v>
-      </c>
-      <c r="O21" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P21" s="5">
@@ -7493,30 +7046,26 @@
       <c r="R21" s="1"/>
       <c r="S21" s="5"/>
       <c r="T21" s="5">
+        <f t="shared" si="11"/>
+        <v>4032</v>
+      </c>
+      <c r="U21" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4032</v>
+      </c>
+      <c r="V21" s="5"/>
+      <c r="W21" s="1"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5">
         <f t="shared" si="12"/>
         <v>4032</v>
       </c>
-      <c r="U21" s="5">
+      <c r="Z21" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V21" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4032</v>
-      </c>
-      <c r="W21" s="5"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="5"/>
-      <c r="Z21" s="5">
-        <f t="shared" si="14"/>
-        <v>4032</v>
-      </c>
-      <c r="AA21" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    </row>
+    <row r="22" spans="1:26" s="7" customFormat="1" ht="19.5">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -7525,12 +7074,11 @@
       <c r="S22" s="5"/>
       <c r="T22" s="13"/>
       <c r="U22" s="13"/>
-      <c r="V22" s="13"/>
-      <c r="Y22" s="5"/>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="13"/>
       <c r="Z22" s="13"/>
-      <c r="AA22" s="13"/>
-    </row>
-    <row r="23" spans="1:27" ht="38.25">
+    </row>
+    <row r="23" spans="1:26" ht="38.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -7575,11 +7123,11 @@
         <v>9</v>
       </c>
       <c r="N23" s="5">
+        <f t="shared" si="9"/>
+        <v>3920</v>
+      </c>
+      <c r="O23" s="5">
         <f t="shared" si="10"/>
-        <v>3920</v>
-      </c>
-      <c r="O23" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P23" s="5">
@@ -7590,30 +7138,26 @@
       <c r="R23" s="1"/>
       <c r="S23" s="5"/>
       <c r="T23" s="5">
+        <f t="shared" si="11"/>
+        <v>4440</v>
+      </c>
+      <c r="U23" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4440</v>
+      </c>
+      <c r="V23" s="5"/>
+      <c r="W23" s="1"/>
+      <c r="X23" s="5"/>
+      <c r="Y23" s="5">
         <f t="shared" si="12"/>
         <v>4440</v>
       </c>
-      <c r="U23" s="5">
+      <c r="Z23" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V23" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4440</v>
-      </c>
-      <c r="W23" s="5"/>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="5"/>
-      <c r="Z23" s="5">
-        <f t="shared" si="14"/>
-        <v>4440</v>
-      </c>
-      <c r="AA23" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="19.5">
+    </row>
+    <row r="24" spans="1:26" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -7658,11 +7202,11 @@
         <v>9</v>
       </c>
       <c r="N24" s="5">
+        <f t="shared" si="9"/>
+        <v>3920</v>
+      </c>
+      <c r="O24" s="5">
         <f t="shared" si="10"/>
-        <v>3920</v>
-      </c>
-      <c r="O24" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P24" s="5">
@@ -7673,30 +7217,26 @@
       <c r="R24" s="1"/>
       <c r="S24" s="5"/>
       <c r="T24" s="5">
+        <f t="shared" si="11"/>
+        <v>4440</v>
+      </c>
+      <c r="U24" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4440</v>
+      </c>
+      <c r="V24" s="5"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="5"/>
+      <c r="Y24" s="5">
         <f t="shared" si="12"/>
         <v>4440</v>
       </c>
-      <c r="U24" s="5">
+      <c r="Z24" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V24" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4440</v>
-      </c>
-      <c r="W24" s="5"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="5"/>
-      <c r="Z24" s="5">
-        <f t="shared" si="14"/>
-        <v>4440</v>
-      </c>
-      <c r="AA24" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="19.5">
+    </row>
+    <row r="25" spans="1:26" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7741,11 +7281,11 @@
         <v>9</v>
       </c>
       <c r="N25" s="5">
+        <f t="shared" si="9"/>
+        <v>3920</v>
+      </c>
+      <c r="O25" s="5">
         <f t="shared" si="10"/>
-        <v>3920</v>
-      </c>
-      <c r="O25" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P25" s="5">
@@ -7756,30 +7296,26 @@
       <c r="R25" s="1"/>
       <c r="S25" s="5"/>
       <c r="T25" s="5">
+        <f t="shared" si="11"/>
+        <v>4440</v>
+      </c>
+      <c r="U25" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4440</v>
+      </c>
+      <c r="V25" s="5"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="5"/>
+      <c r="Y25" s="5">
         <f t="shared" si="12"/>
         <v>4440</v>
       </c>
-      <c r="U25" s="5">
+      <c r="Z25" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V25" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4440</v>
-      </c>
-      <c r="W25" s="5"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="5"/>
-      <c r="Z25" s="5">
-        <f t="shared" si="14"/>
-        <v>4440</v>
-      </c>
-      <c r="AA25" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="19.5">
+    </row>
+    <row r="26" spans="1:26" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7824,11 +7360,11 @@
         <v>9</v>
       </c>
       <c r="N26" s="5">
+        <f t="shared" si="9"/>
+        <v>3920</v>
+      </c>
+      <c r="O26" s="5">
         <f t="shared" si="10"/>
-        <v>3920</v>
-      </c>
-      <c r="O26" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P26" s="5">
@@ -7839,30 +7375,26 @@
       <c r="R26" s="1"/>
       <c r="S26" s="5"/>
       <c r="T26" s="5">
+        <f t="shared" si="11"/>
+        <v>4440</v>
+      </c>
+      <c r="U26" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4440</v>
+      </c>
+      <c r="V26" s="5"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="5"/>
+      <c r="Y26" s="5">
         <f t="shared" si="12"/>
         <v>4440</v>
       </c>
-      <c r="U26" s="5">
+      <c r="Z26" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V26" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4440</v>
-      </c>
-      <c r="W26" s="5"/>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="5"/>
-      <c r="Z26" s="5">
-        <f t="shared" si="14"/>
-        <v>4440</v>
-      </c>
-      <c r="AA26" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="19.5">
+    </row>
+    <row r="27" spans="1:26" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7907,11 +7439,11 @@
         <v>9</v>
       </c>
       <c r="N27" s="5">
+        <f t="shared" si="9"/>
+        <v>3920</v>
+      </c>
+      <c r="O27" s="5">
         <f t="shared" si="10"/>
-        <v>3920</v>
-      </c>
-      <c r="O27" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P27" s="5">
@@ -7922,30 +7454,26 @@
       <c r="R27" s="1"/>
       <c r="S27" s="5"/>
       <c r="T27" s="5">
+        <f t="shared" si="11"/>
+        <v>4440</v>
+      </c>
+      <c r="U27" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4440</v>
+      </c>
+      <c r="V27" s="5"/>
+      <c r="W27" s="1"/>
+      <c r="X27" s="5"/>
+      <c r="Y27" s="5">
         <f t="shared" si="12"/>
         <v>4440</v>
       </c>
-      <c r="U27" s="5">
+      <c r="Z27" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V27" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4440</v>
-      </c>
-      <c r="W27" s="5"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="5"/>
-      <c r="Z27" s="5">
-        <f t="shared" si="14"/>
-        <v>4440</v>
-      </c>
-      <c r="AA27" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="19.5">
+    </row>
+    <row r="28" spans="1:26" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7990,11 +7518,11 @@
         <v>9</v>
       </c>
       <c r="N28" s="5">
+        <f t="shared" si="9"/>
+        <v>3920</v>
+      </c>
+      <c r="O28" s="5">
         <f t="shared" si="10"/>
-        <v>3920</v>
-      </c>
-      <c r="O28" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P28" s="5">
@@ -8005,30 +7533,26 @@
       <c r="R28" s="1"/>
       <c r="S28" s="5"/>
       <c r="T28" s="5">
+        <f t="shared" si="11"/>
+        <v>4440</v>
+      </c>
+      <c r="U28" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4440</v>
+      </c>
+      <c r="V28" s="5"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="5"/>
+      <c r="Y28" s="5">
         <f t="shared" si="12"/>
         <v>4440</v>
       </c>
-      <c r="U28" s="5">
+      <c r="Z28" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V28" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4440</v>
-      </c>
-      <c r="W28" s="5"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="5"/>
-      <c r="Z28" s="5">
-        <f t="shared" si="14"/>
-        <v>4440</v>
-      </c>
-      <c r="AA28" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="19.5">
+    </row>
+    <row r="29" spans="1:26" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -8073,11 +7597,11 @@
         <v>9</v>
       </c>
       <c r="N29" s="5">
+        <f t="shared" si="9"/>
+        <v>3920</v>
+      </c>
+      <c r="O29" s="5">
         <f t="shared" si="10"/>
-        <v>3920</v>
-      </c>
-      <c r="O29" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P29" s="5">
@@ -8088,30 +7612,26 @@
       <c r="R29" s="1"/>
       <c r="S29" s="5"/>
       <c r="T29" s="5">
+        <f t="shared" si="11"/>
+        <v>4440</v>
+      </c>
+      <c r="U29" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4440</v>
+      </c>
+      <c r="V29" s="5"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="5"/>
+      <c r="Y29" s="5">
         <f t="shared" si="12"/>
         <v>4440</v>
       </c>
-      <c r="U29" s="5">
+      <c r="Z29" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V29" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4440</v>
-      </c>
-      <c r="W29" s="5"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="5"/>
-      <c r="Z29" s="5">
-        <f t="shared" si="14"/>
-        <v>4440</v>
-      </c>
-      <c r="AA29" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="19.5">
+    </row>
+    <row r="30" spans="1:26" ht="19.5">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -8156,11 +7676,11 @@
         <v>9</v>
       </c>
       <c r="N30" s="5">
+        <f t="shared" si="9"/>
+        <v>3920</v>
+      </c>
+      <c r="O30" s="5">
         <f t="shared" si="10"/>
-        <v>3920</v>
-      </c>
-      <c r="O30" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P30" s="5">
@@ -8171,35 +7691,31 @@
       <c r="R30" s="1"/>
       <c r="S30" s="5"/>
       <c r="T30" s="5">
+        <f t="shared" si="11"/>
+        <v>4440</v>
+      </c>
+      <c r="U30" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4440</v>
+      </c>
+      <c r="V30" s="5"/>
+      <c r="W30" s="1"/>
+      <c r="X30" s="5"/>
+      <c r="Y30" s="5">
         <f t="shared" si="12"/>
         <v>4440</v>
       </c>
-      <c r="U30" s="5">
+      <c r="Z30" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V30" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4440</v>
-      </c>
-      <c r="W30" s="5"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="5"/>
-      <c r="Z30" s="5">
-        <f t="shared" si="14"/>
-        <v>4440</v>
-      </c>
-      <c r="AA30" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" ht="19.5">
+    </row>
+    <row r="31" spans="1:26" ht="19.5">
       <c r="A31" s="1">
         <v>3</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C31" s="1">
         <v>555</v>
@@ -8239,11 +7755,11 @@
         <v>9</v>
       </c>
       <c r="N31" s="5">
+        <f t="shared" si="9"/>
+        <v>3920</v>
+      </c>
+      <c r="O31" s="5">
         <f t="shared" si="10"/>
-        <v>3920</v>
-      </c>
-      <c r="O31" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P31" s="5">
@@ -8254,30 +7770,26 @@
       <c r="R31" s="1"/>
       <c r="S31" s="5"/>
       <c r="T31" s="5">
+        <f t="shared" si="11"/>
+        <v>4440</v>
+      </c>
+      <c r="U31" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4440</v>
+      </c>
+      <c r="V31" s="5"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="5"/>
+      <c r="Y31" s="5">
         <f t="shared" si="12"/>
         <v>4440</v>
       </c>
-      <c r="U31" s="5">
+      <c r="Z31" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V31" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4440</v>
-      </c>
-      <c r="W31" s="5"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="5"/>
-      <c r="Z31" s="5">
-        <f t="shared" si="14"/>
-        <v>4440</v>
-      </c>
-      <c r="AA31" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.5">
+    </row>
+    <row r="32" spans="1:26" s="7" customFormat="1" ht="19.5">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -8286,12 +7798,11 @@
       <c r="S32" s="5"/>
       <c r="T32" s="13"/>
       <c r="U32" s="13"/>
-      <c r="V32" s="13"/>
-      <c r="Y32" s="5"/>
+      <c r="X32" s="5"/>
+      <c r="Y32" s="13"/>
       <c r="Z32" s="13"/>
-      <c r="AA32" s="13"/>
-    </row>
-    <row r="33" spans="1:27" ht="19.5">
+    </row>
+    <row r="33" spans="1:26" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -8336,11 +7847,11 @@
         <v>9</v>
       </c>
       <c r="N33" s="5">
+        <f t="shared" si="9"/>
+        <v>3759</v>
+      </c>
+      <c r="O33" s="5">
         <f t="shared" si="10"/>
-        <v>3759</v>
-      </c>
-      <c r="O33" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P33" s="5">
@@ -8351,30 +7862,26 @@
       <c r="R33" s="1"/>
       <c r="S33" s="5"/>
       <c r="T33" s="5">
+        <f t="shared" si="11"/>
+        <v>4320</v>
+      </c>
+      <c r="U33" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4320</v>
+      </c>
+      <c r="V33" s="5"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="5"/>
+      <c r="Y33" s="5">
         <f t="shared" si="12"/>
         <v>4320</v>
       </c>
-      <c r="U33" s="5">
+      <c r="Z33" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V33" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4320</v>
-      </c>
-      <c r="W33" s="5"/>
-      <c r="X33" s="1"/>
-      <c r="Y33" s="5"/>
-      <c r="Z33" s="5">
-        <f t="shared" si="14"/>
-        <v>4320</v>
-      </c>
-      <c r="AA33" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="19.5">
+    </row>
+    <row r="34" spans="1:26" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -8419,11 +7926,11 @@
         <v>9</v>
       </c>
       <c r="N34" s="5">
+        <f t="shared" si="9"/>
+        <v>3759</v>
+      </c>
+      <c r="O34" s="5">
         <f t="shared" si="10"/>
-        <v>3759</v>
-      </c>
-      <c r="O34" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P34" s="5">
@@ -8434,30 +7941,26 @@
       <c r="R34" s="1"/>
       <c r="S34" s="5"/>
       <c r="T34" s="5">
+        <f t="shared" si="11"/>
+        <v>4320</v>
+      </c>
+      <c r="U34" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4320</v>
+      </c>
+      <c r="V34" s="5"/>
+      <c r="W34" s="1"/>
+      <c r="X34" s="5"/>
+      <c r="Y34" s="5">
         <f t="shared" si="12"/>
         <v>4320</v>
       </c>
-      <c r="U34" s="5">
+      <c r="Z34" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V34" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4320</v>
-      </c>
-      <c r="W34" s="5"/>
-      <c r="X34" s="1"/>
-      <c r="Y34" s="5"/>
-      <c r="Z34" s="5">
-        <f t="shared" si="14"/>
-        <v>4320</v>
-      </c>
-      <c r="AA34" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" ht="19.5">
+    </row>
+    <row r="35" spans="1:26" ht="19.5">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -8502,11 +8005,11 @@
         <v>9</v>
       </c>
       <c r="N35" s="5">
+        <f t="shared" si="9"/>
+        <v>3759</v>
+      </c>
+      <c r="O35" s="5">
         <f t="shared" si="10"/>
-        <v>3759</v>
-      </c>
-      <c r="O35" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P35" s="5">
@@ -8517,30 +8020,26 @@
       <c r="R35" s="1"/>
       <c r="S35" s="5"/>
       <c r="T35" s="5">
+        <f t="shared" si="11"/>
+        <v>4320</v>
+      </c>
+      <c r="U35" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4320</v>
+      </c>
+      <c r="V35" s="5"/>
+      <c r="W35" s="1"/>
+      <c r="X35" s="5"/>
+      <c r="Y35" s="5">
         <f t="shared" si="12"/>
         <v>4320</v>
       </c>
-      <c r="U35" s="5">
+      <c r="Z35" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V35" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4320</v>
-      </c>
-      <c r="W35" s="5"/>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="5"/>
-      <c r="Z35" s="5">
-        <f t="shared" si="14"/>
-        <v>4320</v>
-      </c>
-      <c r="AA35" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" ht="19.5">
+    </row>
+    <row r="36" spans="1:26" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -8585,11 +8084,11 @@
         <v>9</v>
       </c>
       <c r="N36" s="5">
+        <f t="shared" si="9"/>
+        <v>3759</v>
+      </c>
+      <c r="O36" s="5">
         <f t="shared" si="10"/>
-        <v>3759</v>
-      </c>
-      <c r="O36" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P36" s="5">
@@ -8600,30 +8099,26 @@
       <c r="R36" s="1"/>
       <c r="S36" s="5"/>
       <c r="T36" s="5">
+        <f t="shared" si="11"/>
+        <v>4320</v>
+      </c>
+      <c r="U36" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4320</v>
+      </c>
+      <c r="V36" s="5"/>
+      <c r="W36" s="1"/>
+      <c r="X36" s="5"/>
+      <c r="Y36" s="5">
         <f t="shared" si="12"/>
         <v>4320</v>
       </c>
-      <c r="U36" s="5">
+      <c r="Z36" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V36" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4320</v>
-      </c>
-      <c r="W36" s="5"/>
-      <c r="X36" s="1"/>
-      <c r="Y36" s="5"/>
-      <c r="Z36" s="5">
-        <f t="shared" si="14"/>
-        <v>4320</v>
-      </c>
-      <c r="AA36" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" ht="38.25">
+    </row>
+    <row r="37" spans="1:26" ht="38.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -8668,11 +8163,11 @@
         <v>9</v>
       </c>
       <c r="N37" s="5">
+        <f t="shared" si="9"/>
+        <v>3759</v>
+      </c>
+      <c r="O37" s="5">
         <f t="shared" si="10"/>
-        <v>3759</v>
-      </c>
-      <c r="O37" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P37" s="5">
@@ -8683,30 +8178,26 @@
       <c r="R37" s="1"/>
       <c r="S37" s="5"/>
       <c r="T37" s="5">
+        <f t="shared" si="11"/>
+        <v>4320</v>
+      </c>
+      <c r="U37" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4320</v>
+      </c>
+      <c r="V37" s="5"/>
+      <c r="W37" s="1"/>
+      <c r="X37" s="5"/>
+      <c r="Y37" s="5">
         <f t="shared" si="12"/>
         <v>4320</v>
       </c>
-      <c r="U37" s="5">
+      <c r="Z37" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V37" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4320</v>
-      </c>
-      <c r="W37" s="5"/>
-      <c r="X37" s="1"/>
-      <c r="Y37" s="5"/>
-      <c r="Z37" s="5">
-        <f t="shared" si="14"/>
-        <v>4320</v>
-      </c>
-      <c r="AA37" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" ht="19.5">
+    </row>
+    <row r="38" spans="1:26" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -8751,11 +8242,11 @@
         <v>9</v>
       </c>
       <c r="N38" s="5">
+        <f t="shared" si="9"/>
+        <v>3759</v>
+      </c>
+      <c r="O38" s="5">
         <f t="shared" si="10"/>
-        <v>3759</v>
-      </c>
-      <c r="O38" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P38" s="5">
@@ -8766,30 +8257,26 @@
       <c r="R38" s="1"/>
       <c r="S38" s="5"/>
       <c r="T38" s="5">
+        <f t="shared" si="11"/>
+        <v>4320</v>
+      </c>
+      <c r="U38" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4320</v>
+      </c>
+      <c r="V38" s="5"/>
+      <c r="W38" s="1"/>
+      <c r="X38" s="5"/>
+      <c r="Y38" s="5">
         <f t="shared" si="12"/>
         <v>4320</v>
       </c>
-      <c r="U38" s="5">
+      <c r="Z38" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V38" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4320</v>
-      </c>
-      <c r="W38" s="5"/>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="5"/>
-      <c r="Z38" s="5">
-        <f t="shared" si="14"/>
-        <v>4320</v>
-      </c>
-      <c r="AA38" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" ht="19.5">
+    </row>
+    <row r="39" spans="1:26" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -8834,11 +8321,11 @@
         <v>9</v>
       </c>
       <c r="N39" s="5">
+        <f t="shared" si="9"/>
+        <v>3759</v>
+      </c>
+      <c r="O39" s="5">
         <f t="shared" si="10"/>
-        <v>3759</v>
-      </c>
-      <c r="O39" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P39" s="5">
@@ -8849,30 +8336,26 @@
       <c r="R39" s="1"/>
       <c r="S39" s="5"/>
       <c r="T39" s="5">
+        <f t="shared" si="11"/>
+        <v>4320</v>
+      </c>
+      <c r="U39" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4320</v>
+      </c>
+      <c r="V39" s="5"/>
+      <c r="W39" s="1"/>
+      <c r="X39" s="5"/>
+      <c r="Y39" s="5">
         <f t="shared" si="12"/>
         <v>4320</v>
       </c>
-      <c r="U39" s="5">
+      <c r="Z39" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V39" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4320</v>
-      </c>
-      <c r="W39" s="5"/>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="5"/>
-      <c r="Z39" s="5">
-        <f t="shared" si="14"/>
-        <v>4320</v>
-      </c>
-      <c r="AA39" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27" ht="19.5">
+    </row>
+    <row r="40" spans="1:26" ht="19.5">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8917,11 +8400,11 @@
         <v>9</v>
       </c>
       <c r="N40" s="5">
+        <f t="shared" si="9"/>
+        <v>3759</v>
+      </c>
+      <c r="O40" s="5">
         <f t="shared" si="10"/>
-        <v>3759</v>
-      </c>
-      <c r="O40" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P40" s="5">
@@ -8932,30 +8415,26 @@
       <c r="R40" s="1"/>
       <c r="S40" s="5"/>
       <c r="T40" s="5">
+        <f t="shared" si="11"/>
+        <v>4320</v>
+      </c>
+      <c r="U40" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4320</v>
+      </c>
+      <c r="V40" s="5"/>
+      <c r="W40" s="1"/>
+      <c r="X40" s="5"/>
+      <c r="Y40" s="5">
         <f t="shared" si="12"/>
         <v>4320</v>
       </c>
-      <c r="U40" s="5">
+      <c r="Z40" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V40" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4320</v>
-      </c>
-      <c r="W40" s="5"/>
-      <c r="X40" s="1"/>
-      <c r="Y40" s="5"/>
-      <c r="Z40" s="5">
-        <f t="shared" si="14"/>
-        <v>4320</v>
-      </c>
-      <c r="AA40" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:27" ht="19.5">
+    </row>
+    <row r="41" spans="1:26" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -9000,11 +8479,11 @@
         <v>9</v>
       </c>
       <c r="N41" s="5">
+        <f t="shared" si="9"/>
+        <v>3759</v>
+      </c>
+      <c r="O41" s="5">
         <f t="shared" si="10"/>
-        <v>3759</v>
-      </c>
-      <c r="O41" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P41" s="5">
@@ -9015,30 +8494,26 @@
       <c r="R41" s="1"/>
       <c r="S41" s="5"/>
       <c r="T41" s="5">
+        <f t="shared" si="11"/>
+        <v>4320</v>
+      </c>
+      <c r="U41" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4320</v>
+      </c>
+      <c r="V41" s="5"/>
+      <c r="W41" s="1"/>
+      <c r="X41" s="5"/>
+      <c r="Y41" s="5">
         <f t="shared" si="12"/>
         <v>4320</v>
       </c>
-      <c r="U41" s="5">
+      <c r="Z41" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V41" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4320</v>
-      </c>
-      <c r="W41" s="5"/>
-      <c r="X41" s="1"/>
-      <c r="Y41" s="5"/>
-      <c r="Z41" s="5">
-        <f t="shared" si="14"/>
-        <v>4320</v>
-      </c>
-      <c r="AA41" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.5">
+    </row>
+    <row r="42" spans="1:26" s="7" customFormat="1" ht="19.5">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -9047,12 +8522,11 @@
       <c r="S42" s="5"/>
       <c r="T42" s="13"/>
       <c r="U42" s="13"/>
-      <c r="V42" s="13"/>
-      <c r="Y42" s="5"/>
+      <c r="X42" s="5"/>
+      <c r="Y42" s="13"/>
       <c r="Z42" s="13"/>
-      <c r="AA42" s="13"/>
-    </row>
-    <row r="43" spans="1:27" ht="19.5">
+    </row>
+    <row r="43" spans="1:26" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -9097,11 +8571,11 @@
         <v>9</v>
       </c>
       <c r="N43" s="5">
+        <f t="shared" si="9"/>
+        <v>3996</v>
+      </c>
+      <c r="O43" s="5">
         <f t="shared" si="10"/>
-        <v>3996</v>
-      </c>
-      <c r="O43" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P43" s="5">
@@ -9112,30 +8586,26 @@
       <c r="R43" s="1"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5">
+        <f t="shared" si="11"/>
+        <v>4568</v>
+      </c>
+      <c r="U43" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4568</v>
+      </c>
+      <c r="V43" s="5"/>
+      <c r="W43" s="1"/>
+      <c r="X43" s="5"/>
+      <c r="Y43" s="5">
         <f t="shared" si="12"/>
         <v>4568</v>
       </c>
-      <c r="U43" s="5">
+      <c r="Z43" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V43" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4568</v>
-      </c>
-      <c r="W43" s="5"/>
-      <c r="X43" s="1"/>
-      <c r="Y43" s="5"/>
-      <c r="Z43" s="5">
-        <f t="shared" si="14"/>
-        <v>4568</v>
-      </c>
-      <c r="AA43" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:27" ht="19.5">
+    </row>
+    <row r="44" spans="1:26" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -9180,11 +8650,11 @@
         <v>9</v>
       </c>
       <c r="N44" s="5">
+        <f t="shared" si="9"/>
+        <v>3996</v>
+      </c>
+      <c r="O44" s="5">
         <f t="shared" si="10"/>
-        <v>3996</v>
-      </c>
-      <c r="O44" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P44" s="5">
@@ -9195,30 +8665,26 @@
       <c r="R44" s="1"/>
       <c r="S44" s="5"/>
       <c r="T44" s="5">
+        <f t="shared" si="11"/>
+        <v>4568</v>
+      </c>
+      <c r="U44" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4568</v>
+      </c>
+      <c r="V44" s="5"/>
+      <c r="W44" s="1"/>
+      <c r="X44" s="5"/>
+      <c r="Y44" s="5">
         <f t="shared" si="12"/>
         <v>4568</v>
       </c>
-      <c r="U44" s="5">
+      <c r="Z44" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V44" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4568</v>
-      </c>
-      <c r="W44" s="5"/>
-      <c r="X44" s="1"/>
-      <c r="Y44" s="5"/>
-      <c r="Z44" s="5">
-        <f t="shared" si="14"/>
-        <v>4568</v>
-      </c>
-      <c r="AA44" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:27" ht="19.5">
+    </row>
+    <row r="45" spans="1:26" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -9263,11 +8729,11 @@
         <v>9</v>
       </c>
       <c r="N45" s="5">
+        <f t="shared" si="9"/>
+        <v>3996</v>
+      </c>
+      <c r="O45" s="5">
         <f t="shared" si="10"/>
-        <v>3996</v>
-      </c>
-      <c r="O45" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P45" s="5">
@@ -9278,30 +8744,26 @@
       <c r="R45" s="1"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5">
+        <f t="shared" si="11"/>
+        <v>4568</v>
+      </c>
+      <c r="U45" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4568</v>
+      </c>
+      <c r="V45" s="5"/>
+      <c r="W45" s="1"/>
+      <c r="X45" s="5"/>
+      <c r="Y45" s="5">
         <f t="shared" si="12"/>
         <v>4568</v>
       </c>
-      <c r="U45" s="5">
+      <c r="Z45" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V45" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4568</v>
-      </c>
-      <c r="W45" s="5"/>
-      <c r="X45" s="1"/>
-      <c r="Y45" s="5"/>
-      <c r="Z45" s="5">
-        <f t="shared" si="14"/>
-        <v>4568</v>
-      </c>
-      <c r="AA45" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:27" ht="19.5">
+    </row>
+    <row r="46" spans="1:26" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -9346,11 +8808,11 @@
         <v>9</v>
       </c>
       <c r="N46" s="5">
+        <f t="shared" si="9"/>
+        <v>3996</v>
+      </c>
+      <c r="O46" s="5">
         <f t="shared" si="10"/>
-        <v>3996</v>
-      </c>
-      <c r="O46" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P46" s="5">
@@ -9361,30 +8823,26 @@
       <c r="R46" s="1"/>
       <c r="S46" s="5"/>
       <c r="T46" s="5">
+        <f t="shared" si="11"/>
+        <v>4568</v>
+      </c>
+      <c r="U46" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4568</v>
+      </c>
+      <c r="V46" s="5"/>
+      <c r="W46" s="1"/>
+      <c r="X46" s="5"/>
+      <c r="Y46" s="5">
         <f t="shared" si="12"/>
         <v>4568</v>
       </c>
-      <c r="U46" s="5">
+      <c r="Z46" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V46" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4568</v>
-      </c>
-      <c r="W46" s="5"/>
-      <c r="X46" s="1"/>
-      <c r="Y46" s="5"/>
-      <c r="Z46" s="5">
-        <f t="shared" si="14"/>
-        <v>4568</v>
-      </c>
-      <c r="AA46" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:27" ht="38.25">
+    </row>
+    <row r="47" spans="1:26" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -9429,11 +8887,11 @@
         <v>9</v>
       </c>
       <c r="N47" s="5">
+        <f t="shared" si="9"/>
+        <v>3996</v>
+      </c>
+      <c r="O47" s="5">
         <f t="shared" si="10"/>
-        <v>3996</v>
-      </c>
-      <c r="O47" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P47" s="5">
@@ -9444,30 +8902,26 @@
       <c r="R47" s="1"/>
       <c r="S47" s="5"/>
       <c r="T47" s="5">
+        <f t="shared" si="11"/>
+        <v>4568</v>
+      </c>
+      <c r="U47" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4568</v>
+      </c>
+      <c r="V47" s="5"/>
+      <c r="W47" s="1"/>
+      <c r="X47" s="5"/>
+      <c r="Y47" s="5">
         <f t="shared" si="12"/>
         <v>4568</v>
       </c>
-      <c r="U47" s="5">
+      <c r="Z47" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V47" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4568</v>
-      </c>
-      <c r="W47" s="5"/>
-      <c r="X47" s="1"/>
-      <c r="Y47" s="5"/>
-      <c r="Z47" s="5">
-        <f t="shared" si="14"/>
-        <v>4568</v>
-      </c>
-      <c r="AA47" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:27" ht="19.5">
+    </row>
+    <row r="48" spans="1:26" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -9512,11 +8966,11 @@
         <v>9</v>
       </c>
       <c r="N48" s="5">
+        <f t="shared" si="9"/>
+        <v>3996</v>
+      </c>
+      <c r="O48" s="5">
         <f t="shared" si="10"/>
-        <v>3996</v>
-      </c>
-      <c r="O48" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P48" s="5">
@@ -9527,30 +8981,26 @@
       <c r="R48" s="1"/>
       <c r="S48" s="5"/>
       <c r="T48" s="5">
+        <f t="shared" si="11"/>
+        <v>4568</v>
+      </c>
+      <c r="U48" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4568</v>
+      </c>
+      <c r="V48" s="5"/>
+      <c r="W48" s="1"/>
+      <c r="X48" s="5"/>
+      <c r="Y48" s="5">
         <f t="shared" si="12"/>
         <v>4568</v>
       </c>
-      <c r="U48" s="5">
+      <c r="Z48" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V48" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4568</v>
-      </c>
-      <c r="W48" s="5"/>
-      <c r="X48" s="1"/>
-      <c r="Y48" s="5"/>
-      <c r="Z48" s="5">
-        <f t="shared" si="14"/>
-        <v>4568</v>
-      </c>
-      <c r="AA48" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:27" ht="19.5">
+    </row>
+    <row r="49" spans="1:26" ht="19.5">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -9595,11 +9045,11 @@
         <v>9</v>
       </c>
       <c r="N49" s="5">
+        <f t="shared" si="9"/>
+        <v>3996</v>
+      </c>
+      <c r="O49" s="5">
         <f t="shared" si="10"/>
-        <v>3996</v>
-      </c>
-      <c r="O49" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P49" s="5">
@@ -9610,30 +9060,26 @@
       <c r="R49" s="1"/>
       <c r="S49" s="5"/>
       <c r="T49" s="5">
+        <f t="shared" si="11"/>
+        <v>4568</v>
+      </c>
+      <c r="U49" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4568</v>
+      </c>
+      <c r="V49" s="5"/>
+      <c r="W49" s="1"/>
+      <c r="X49" s="5"/>
+      <c r="Y49" s="5">
         <f t="shared" si="12"/>
         <v>4568</v>
       </c>
-      <c r="U49" s="5">
+      <c r="Z49" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V49" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4568</v>
-      </c>
-      <c r="W49" s="5"/>
-      <c r="X49" s="1"/>
-      <c r="Y49" s="5"/>
-      <c r="Z49" s="5">
-        <f t="shared" si="14"/>
-        <v>4568</v>
-      </c>
-      <c r="AA49" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:27" ht="19.5">
+    </row>
+    <row r="50" spans="1:26" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -9678,11 +9124,11 @@
         <v>9</v>
       </c>
       <c r="N50" s="5">
+        <f t="shared" si="9"/>
+        <v>3996</v>
+      </c>
+      <c r="O50" s="5">
         <f t="shared" si="10"/>
-        <v>3996</v>
-      </c>
-      <c r="O50" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P50" s="5">
@@ -9693,30 +9139,26 @@
       <c r="R50" s="1"/>
       <c r="S50" s="5"/>
       <c r="T50" s="5">
+        <f t="shared" si="11"/>
+        <v>4568</v>
+      </c>
+      <c r="U50" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4568</v>
+      </c>
+      <c r="V50" s="5"/>
+      <c r="W50" s="1"/>
+      <c r="X50" s="5"/>
+      <c r="Y50" s="5">
         <f t="shared" si="12"/>
         <v>4568</v>
       </c>
-      <c r="U50" s="5">
+      <c r="Z50" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V50" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4568</v>
-      </c>
-      <c r="W50" s="5"/>
-      <c r="X50" s="1"/>
-      <c r="Y50" s="5"/>
-      <c r="Z50" s="5">
-        <f t="shared" si="14"/>
-        <v>4568</v>
-      </c>
-      <c r="AA50" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:27" ht="19.5">
+    </row>
+    <row r="51" spans="1:26" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -9761,11 +9203,11 @@
         <v>9</v>
       </c>
       <c r="N51" s="5">
+        <f t="shared" si="9"/>
+        <v>3996</v>
+      </c>
+      <c r="O51" s="5">
         <f t="shared" si="10"/>
-        <v>3996</v>
-      </c>
-      <c r="O51" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P51" s="5">
@@ -9776,30 +9218,26 @@
       <c r="R51" s="1"/>
       <c r="S51" s="5"/>
       <c r="T51" s="5">
+        <f t="shared" si="11"/>
+        <v>4568</v>
+      </c>
+      <c r="U51" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4568</v>
+      </c>
+      <c r="V51" s="5"/>
+      <c r="W51" s="1"/>
+      <c r="X51" s="5"/>
+      <c r="Y51" s="5">
         <f t="shared" si="12"/>
         <v>4568</v>
       </c>
-      <c r="U51" s="5">
+      <c r="Z51" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V51" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4568</v>
-      </c>
-      <c r="W51" s="5"/>
-      <c r="X51" s="1"/>
-      <c r="Y51" s="5"/>
-      <c r="Z51" s="5">
-        <f t="shared" si="14"/>
-        <v>4568</v>
-      </c>
-      <c r="AA51" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    </row>
+    <row r="52" spans="1:26" s="7" customFormat="1" ht="19.5">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -9808,12 +9246,11 @@
       <c r="S52" s="5"/>
       <c r="T52" s="13"/>
       <c r="U52" s="13"/>
-      <c r="V52" s="13"/>
-      <c r="Y52" s="5"/>
+      <c r="X52" s="5"/>
+      <c r="Y52" s="13"/>
       <c r="Z52" s="13"/>
-      <c r="AA52" s="13"/>
-    </row>
-    <row r="53" spans="1:27" ht="19.5">
+    </row>
+    <row r="53" spans="1:26" ht="19.5">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -9852,11 +9289,11 @@
       <c r="L53" s="1"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5">
+        <f t="shared" si="9"/>
+        <v>4080</v>
+      </c>
+      <c r="O53" s="5">
         <f t="shared" si="10"/>
-        <v>4080</v>
-      </c>
-      <c r="O53" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P53" s="5">
@@ -9867,30 +9304,26 @@
       <c r="R53" s="1"/>
       <c r="S53" s="5"/>
       <c r="T53" s="5">
+        <f t="shared" si="11"/>
+        <v>4080</v>
+      </c>
+      <c r="U53" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4080</v>
+      </c>
+      <c r="V53" s="5"/>
+      <c r="W53" s="1"/>
+      <c r="X53" s="5"/>
+      <c r="Y53" s="5">
         <f t="shared" si="12"/>
         <v>4080</v>
       </c>
-      <c r="U53" s="5">
+      <c r="Z53" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V53" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4080</v>
-      </c>
-      <c r="W53" s="5"/>
-      <c r="X53" s="1"/>
-      <c r="Y53" s="5"/>
-      <c r="Z53" s="5">
-        <f t="shared" si="14"/>
-        <v>4080</v>
-      </c>
-      <c r="AA53" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:27" ht="19.5">
+    </row>
+    <row r="54" spans="1:26" ht="19.5">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -9929,11 +9362,11 @@
       <c r="L54" s="1"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5">
+        <f t="shared" si="9"/>
+        <v>4080</v>
+      </c>
+      <c r="O54" s="5">
         <f t="shared" si="10"/>
-        <v>4080</v>
-      </c>
-      <c r="O54" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P54" s="5">
@@ -9944,30 +9377,26 @@
       <c r="R54" s="1"/>
       <c r="S54" s="5"/>
       <c r="T54" s="5">
+        <f t="shared" si="11"/>
+        <v>4080</v>
+      </c>
+      <c r="U54" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4080</v>
+      </c>
+      <c r="V54" s="5"/>
+      <c r="W54" s="1"/>
+      <c r="X54" s="5"/>
+      <c r="Y54" s="5">
         <f t="shared" si="12"/>
         <v>4080</v>
       </c>
-      <c r="U54" s="5">
+      <c r="Z54" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V54" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4080</v>
-      </c>
-      <c r="W54" s="5"/>
-      <c r="X54" s="1"/>
-      <c r="Y54" s="5"/>
-      <c r="Z54" s="5">
-        <f t="shared" si="14"/>
-        <v>4080</v>
-      </c>
-      <c r="AA54" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:27" ht="19.5">
+    </row>
+    <row r="55" spans="1:26" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -10006,11 +9435,11 @@
       <c r="L55" s="1"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5">
+        <f t="shared" si="9"/>
+        <v>4080</v>
+      </c>
+      <c r="O55" s="5">
         <f t="shared" si="10"/>
-        <v>4080</v>
-      </c>
-      <c r="O55" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P55" s="5">
@@ -10021,30 +9450,26 @@
       <c r="R55" s="1"/>
       <c r="S55" s="5"/>
       <c r="T55" s="5">
+        <f t="shared" si="11"/>
+        <v>4080</v>
+      </c>
+      <c r="U55" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4080</v>
+      </c>
+      <c r="V55" s="5"/>
+      <c r="W55" s="1"/>
+      <c r="X55" s="5"/>
+      <c r="Y55" s="5">
         <f t="shared" si="12"/>
         <v>4080</v>
       </c>
-      <c r="U55" s="5">
+      <c r="Z55" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V55" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4080</v>
-      </c>
-      <c r="W55" s="5"/>
-      <c r="X55" s="1"/>
-      <c r="Y55" s="5"/>
-      <c r="Z55" s="5">
-        <f t="shared" si="14"/>
-        <v>4080</v>
-      </c>
-      <c r="AA55" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:27" ht="19.5">
+    </row>
+    <row r="56" spans="1:26" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -10083,11 +9508,11 @@
       <c r="L56" s="1"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5">
+        <f t="shared" si="9"/>
+        <v>4080</v>
+      </c>
+      <c r="O56" s="5">
         <f t="shared" si="10"/>
-        <v>4080</v>
-      </c>
-      <c r="O56" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P56" s="5">
@@ -10098,30 +9523,26 @@
       <c r="R56" s="1"/>
       <c r="S56" s="5"/>
       <c r="T56" s="5">
+        <f t="shared" si="11"/>
+        <v>4080</v>
+      </c>
+      <c r="U56" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4080</v>
+      </c>
+      <c r="V56" s="5"/>
+      <c r="W56" s="1"/>
+      <c r="X56" s="5"/>
+      <c r="Y56" s="5">
         <f t="shared" si="12"/>
         <v>4080</v>
       </c>
-      <c r="U56" s="5">
+      <c r="Z56" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V56" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4080</v>
-      </c>
-      <c r="W56" s="5"/>
-      <c r="X56" s="1"/>
-      <c r="Y56" s="5"/>
-      <c r="Z56" s="5">
-        <f t="shared" si="14"/>
-        <v>4080</v>
-      </c>
-      <c r="AA56" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:27" ht="38.25">
+    </row>
+    <row r="57" spans="1:26" ht="38.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -10160,11 +9581,11 @@
       <c r="L57" s="1"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5">
+        <f t="shared" si="9"/>
+        <v>4080</v>
+      </c>
+      <c r="O57" s="5">
         <f t="shared" si="10"/>
-        <v>4080</v>
-      </c>
-      <c r="O57" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P57" s="5">
@@ -10175,30 +9596,26 @@
       <c r="R57" s="1"/>
       <c r="S57" s="5"/>
       <c r="T57" s="5">
+        <f t="shared" si="11"/>
+        <v>4080</v>
+      </c>
+      <c r="U57" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4080</v>
+      </c>
+      <c r="V57" s="5"/>
+      <c r="W57" s="1"/>
+      <c r="X57" s="5"/>
+      <c r="Y57" s="5">
         <f t="shared" si="12"/>
         <v>4080</v>
       </c>
-      <c r="U57" s="5">
+      <c r="Z57" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V57" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4080</v>
-      </c>
-      <c r="W57" s="5"/>
-      <c r="X57" s="1"/>
-      <c r="Y57" s="5"/>
-      <c r="Z57" s="5">
-        <f t="shared" si="14"/>
-        <v>4080</v>
-      </c>
-      <c r="AA57" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:27" ht="19.5">
+    </row>
+    <row r="58" spans="1:26" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -10237,11 +9654,11 @@
       <c r="L58" s="1"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5">
+        <f t="shared" si="9"/>
+        <v>4080</v>
+      </c>
+      <c r="O58" s="5">
         <f t="shared" si="10"/>
-        <v>4080</v>
-      </c>
-      <c r="O58" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P58" s="5">
@@ -10252,30 +9669,26 @@
       <c r="R58" s="1"/>
       <c r="S58" s="5"/>
       <c r="T58" s="5">
+        <f t="shared" si="11"/>
+        <v>4080</v>
+      </c>
+      <c r="U58" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4080</v>
+      </c>
+      <c r="V58" s="5"/>
+      <c r="W58" s="1"/>
+      <c r="X58" s="5"/>
+      <c r="Y58" s="5">
         <f t="shared" si="12"/>
         <v>4080</v>
       </c>
-      <c r="U58" s="5">
+      <c r="Z58" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V58" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4080</v>
-      </c>
-      <c r="W58" s="5"/>
-      <c r="X58" s="1"/>
-      <c r="Y58" s="5"/>
-      <c r="Z58" s="5">
-        <f t="shared" si="14"/>
-        <v>4080</v>
-      </c>
-      <c r="AA58" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:27" ht="19.5">
+    </row>
+    <row r="59" spans="1:26" ht="19.5">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -10314,11 +9727,11 @@
       <c r="L59" s="1"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5">
+        <f t="shared" si="9"/>
+        <v>4080</v>
+      </c>
+      <c r="O59" s="5">
         <f t="shared" si="10"/>
-        <v>4080</v>
-      </c>
-      <c r="O59" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P59" s="5">
@@ -10329,30 +9742,26 @@
       <c r="R59" s="1"/>
       <c r="S59" s="5"/>
       <c r="T59" s="5">
+        <f t="shared" si="11"/>
+        <v>4080</v>
+      </c>
+      <c r="U59" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4080</v>
+      </c>
+      <c r="V59" s="5"/>
+      <c r="W59" s="1"/>
+      <c r="X59" s="5"/>
+      <c r="Y59" s="5">
         <f t="shared" si="12"/>
         <v>4080</v>
       </c>
-      <c r="U59" s="5">
+      <c r="Z59" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V59" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4080</v>
-      </c>
-      <c r="W59" s="5"/>
-      <c r="X59" s="1"/>
-      <c r="Y59" s="5"/>
-      <c r="Z59" s="5">
-        <f t="shared" si="14"/>
-        <v>4080</v>
-      </c>
-      <c r="AA59" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:27" ht="19.5">
+    </row>
+    <row r="60" spans="1:26" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -10391,11 +9800,11 @@
       <c r="L60" s="1"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5">
+        <f t="shared" si="9"/>
+        <v>4080</v>
+      </c>
+      <c r="O60" s="5">
         <f t="shared" si="10"/>
-        <v>4080</v>
-      </c>
-      <c r="O60" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P60" s="5">
@@ -10406,30 +9815,26 @@
       <c r="R60" s="1"/>
       <c r="S60" s="5"/>
       <c r="T60" s="5">
+        <f t="shared" si="11"/>
+        <v>4080</v>
+      </c>
+      <c r="U60" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4080</v>
+      </c>
+      <c r="V60" s="5"/>
+      <c r="W60" s="1"/>
+      <c r="X60" s="5"/>
+      <c r="Y60" s="5">
         <f t="shared" si="12"/>
         <v>4080</v>
       </c>
-      <c r="U60" s="5">
+      <c r="Z60" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V60" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4080</v>
-      </c>
-      <c r="W60" s="5"/>
-      <c r="X60" s="1"/>
-      <c r="Y60" s="5"/>
-      <c r="Z60" s="5">
-        <f t="shared" si="14"/>
-        <v>4080</v>
-      </c>
-      <c r="AA60" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:27" ht="19.5">
+    </row>
+    <row r="61" spans="1:26" ht="19.5">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -10468,11 +9873,11 @@
       <c r="L61" s="1"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5">
+        <f t="shared" si="9"/>
+        <v>4080</v>
+      </c>
+      <c r="O61" s="5">
         <f t="shared" si="10"/>
-        <v>4080</v>
-      </c>
-      <c r="O61" s="5">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P61" s="5">
@@ -10483,30 +9888,26 @@
       <c r="R61" s="1"/>
       <c r="S61" s="5"/>
       <c r="T61" s="5">
+        <f t="shared" si="11"/>
+        <v>4080</v>
+      </c>
+      <c r="U61" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4080</v>
+      </c>
+      <c r="V61" s="5"/>
+      <c r="W61" s="1"/>
+      <c r="X61" s="5"/>
+      <c r="Y61" s="5">
         <f t="shared" si="12"/>
         <v>4080</v>
       </c>
-      <c r="U61" s="5">
+      <c r="Z61" s="5">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V61" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4080</v>
-      </c>
-      <c r="W61" s="5"/>
-      <c r="X61" s="1"/>
-      <c r="Y61" s="5"/>
-      <c r="Z61" s="5">
-        <f t="shared" si="14"/>
-        <v>4080</v>
-      </c>
-      <c r="AA61" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    </row>
+    <row r="62" spans="1:26" s="7" customFormat="1" ht="19.5">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -10515,12 +9916,11 @@
       <c r="S62" s="5"/>
       <c r="T62" s="13"/>
       <c r="U62" s="13"/>
-      <c r="V62" s="13"/>
-      <c r="Y62" s="5"/>
+      <c r="X62" s="5"/>
+      <c r="Y62" s="13"/>
       <c r="Z62" s="13"/>
-      <c r="AA62" s="13"/>
-    </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    </row>
+    <row r="63" spans="1:26" ht="19.5">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -10551,11 +9951,11 @@
       <c r="L63" s="10"/>
       <c r="M63" s="12"/>
       <c r="N63" s="12">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O63" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O63" s="12">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P63" s="12">
@@ -10566,30 +9966,26 @@
       <c r="R63" s="10"/>
       <c r="S63" s="12"/>
       <c r="T63" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U63" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V63" s="12"/>
+      <c r="W63" s="10"/>
+      <c r="X63" s="12"/>
+      <c r="Y63" s="12">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="U63" s="12">
+      <c r="Z63" s="12">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V63" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W63" s="12"/>
-      <c r="X63" s="10"/>
-      <c r="Y63" s="12"/>
-      <c r="Z63" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA63" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:27" ht="19.5">
+    </row>
+    <row r="64" spans="1:26" ht="19.5">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -10620,11 +10016,11 @@
       <c r="L64" s="10"/>
       <c r="M64" s="12"/>
       <c r="N64" s="12">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O64" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O64" s="12">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P64" s="12">
@@ -10635,30 +10031,26 @@
       <c r="R64" s="10"/>
       <c r="S64" s="12"/>
       <c r="T64" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U64" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V64" s="12"/>
+      <c r="W64" s="10"/>
+      <c r="X64" s="12"/>
+      <c r="Y64" s="12">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="U64" s="12">
+      <c r="Z64" s="12">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V64" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W64" s="12"/>
-      <c r="X64" s="10"/>
-      <c r="Y64" s="12"/>
-      <c r="Z64" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA64" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:27" ht="19.5">
+    </row>
+    <row r="65" spans="1:26" ht="19.5">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -10689,11 +10081,11 @@
       <c r="L65" s="10"/>
       <c r="M65" s="12"/>
       <c r="N65" s="12">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O65" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O65" s="12">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P65" s="12">
@@ -10704,30 +10096,26 @@
       <c r="R65" s="10"/>
       <c r="S65" s="12"/>
       <c r="T65" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U65" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V65" s="12"/>
+      <c r="W65" s="10"/>
+      <c r="X65" s="12"/>
+      <c r="Y65" s="12">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="U65" s="12">
+      <c r="Z65" s="12">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V65" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W65" s="12"/>
-      <c r="X65" s="10"/>
-      <c r="Y65" s="12"/>
-      <c r="Z65" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA65" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:27" ht="19.5">
+    </row>
+    <row r="66" spans="1:26" ht="19.5">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -10758,11 +10146,11 @@
       <c r="L66" s="10"/>
       <c r="M66" s="12"/>
       <c r="N66" s="12">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O66" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O66" s="12">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P66" s="12">
@@ -10773,30 +10161,26 @@
       <c r="R66" s="10"/>
       <c r="S66" s="12"/>
       <c r="T66" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U66" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V66" s="12"/>
+      <c r="W66" s="10"/>
+      <c r="X66" s="12"/>
+      <c r="Y66" s="12">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="U66" s="12">
+      <c r="Z66" s="12">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V66" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W66" s="12"/>
-      <c r="X66" s="10"/>
-      <c r="Y66" s="12"/>
-      <c r="Z66" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA66" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:27" ht="38.25">
+    </row>
+    <row r="67" spans="1:26" ht="38.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -10827,11 +10211,11 @@
       <c r="L67" s="10"/>
       <c r="M67" s="12"/>
       <c r="N67" s="12">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O67" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O67" s="12">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P67" s="12">
@@ -10842,30 +10226,26 @@
       <c r="R67" s="10"/>
       <c r="S67" s="12"/>
       <c r="T67" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U67" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V67" s="12"/>
+      <c r="W67" s="10"/>
+      <c r="X67" s="12"/>
+      <c r="Y67" s="12">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="U67" s="12">
+      <c r="Z67" s="12">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V67" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W67" s="12"/>
-      <c r="X67" s="10"/>
-      <c r="Y67" s="12"/>
-      <c r="Z67" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA67" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:27" ht="19.5">
+    </row>
+    <row r="68" spans="1:26" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -10896,11 +10276,11 @@
       <c r="L68" s="10"/>
       <c r="M68" s="12"/>
       <c r="N68" s="12">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O68" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O68" s="12">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P68" s="12">
@@ -10911,30 +10291,26 @@
       <c r="R68" s="10"/>
       <c r="S68" s="12"/>
       <c r="T68" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U68" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V68" s="12"/>
+      <c r="W68" s="10"/>
+      <c r="X68" s="12"/>
+      <c r="Y68" s="12">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="U68" s="12">
+      <c r="Z68" s="12">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V68" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W68" s="12"/>
-      <c r="X68" s="10"/>
-      <c r="Y68" s="12"/>
-      <c r="Z68" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA68" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:27" ht="19.5">
+    </row>
+    <row r="69" spans="1:26" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -10965,11 +10341,11 @@
       <c r="L69" s="10"/>
       <c r="M69" s="12"/>
       <c r="N69" s="12">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O69" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O69" s="12">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P69" s="12">
@@ -10980,30 +10356,26 @@
       <c r="R69" s="10"/>
       <c r="S69" s="12"/>
       <c r="T69" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U69" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V69" s="12"/>
+      <c r="W69" s="10"/>
+      <c r="X69" s="12"/>
+      <c r="Y69" s="12">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="U69" s="12">
+      <c r="Z69" s="12">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V69" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W69" s="12"/>
-      <c r="X69" s="10"/>
-      <c r="Y69" s="12"/>
-      <c r="Z69" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AA69" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:27" ht="19.5">
+    </row>
+    <row r="70" spans="1:26" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -11034,11 +10406,11 @@
       <c r="L70" s="10"/>
       <c r="M70" s="12"/>
       <c r="N70" s="12">
-        <f t="shared" ref="N70:N126" si="16">IF((J70-K70)&lt;0,0,(J70-K70))</f>
+        <f t="shared" ref="N70:N126" si="14">IF((J70-K70)&lt;0,0,(J70-K70))</f>
         <v>0</v>
       </c>
       <c r="O70" s="12">
-        <f t="shared" ref="O70:O126" si="17">IF((K70-J70)&lt;0,0,(K70-J70))</f>
+        <f t="shared" ref="O70:O126" si="15">IF((K70-J70)&lt;0,0,(K70-J70))</f>
         <v>0</v>
       </c>
       <c r="P70" s="12">
@@ -11049,30 +10421,26 @@
       <c r="R70" s="10"/>
       <c r="S70" s="12"/>
       <c r="T70" s="12">
-        <f t="shared" ref="T70:T127" si="18">IF((P70-Q70)&lt;0,0,(P70-Q70))</f>
+        <f t="shared" ref="T70:T127" si="16">IF((P70-Q70)&lt;0,0,(P70-Q70))</f>
         <v>0</v>
       </c>
       <c r="U70" s="12">
-        <f t="shared" ref="U70:U127" si="19">IF((Q70-P70)&lt;0,0,(Q70-P70))</f>
-        <v>0</v>
-      </c>
-      <c r="V70" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W70" s="12"/>
-      <c r="X70" s="10"/>
-      <c r="Y70" s="12"/>
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V70" s="12"/>
+      <c r="W70" s="10"/>
+      <c r="X70" s="12"/>
+      <c r="Y70" s="12">
+        <f t="shared" ref="Y70:Y127" si="17">IF((U70-V70)&lt;0,0,(U70-V70))</f>
+        <v>0</v>
+      </c>
       <c r="Z70" s="12">
-        <f t="shared" ref="Z70:Z127" si="20">IF((V70-W70)&lt;0,0,(V70-W70))</f>
-        <v>0</v>
-      </c>
-      <c r="AA70" s="12">
-        <f t="shared" ref="AA70:AA127" si="21">IF((W70-V70)&lt;0,0,(W70-V70))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:27" ht="19.5">
+        <f t="shared" ref="Z70:Z127" si="18">IF((V70-U70)&lt;0,0,(V70-U70))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:26" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -11103,11 +10471,11 @@
       <c r="L71" s="10"/>
       <c r="M71" s="12"/>
       <c r="N71" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O71" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P71" s="12">
@@ -11118,30 +10486,26 @@
       <c r="R71" s="10"/>
       <c r="S71" s="12"/>
       <c r="T71" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U71" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V71" s="12"/>
+      <c r="W71" s="10"/>
+      <c r="X71" s="12"/>
+      <c r="Y71" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z71" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U71" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V71" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W71" s="12"/>
-      <c r="X71" s="10"/>
-      <c r="Y71" s="12"/>
-      <c r="Z71" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA71" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    </row>
+    <row r="72" spans="1:26" s="7" customFormat="1" ht="19.5">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -11150,12 +10514,11 @@
       <c r="S72" s="5"/>
       <c r="T72" s="13"/>
       <c r="U72" s="13"/>
-      <c r="V72" s="13"/>
-      <c r="Y72" s="5"/>
+      <c r="X72" s="5"/>
+      <c r="Y72" s="13"/>
       <c r="Z72" s="13"/>
-      <c r="AA72" s="13"/>
-    </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    </row>
+    <row r="73" spans="1:26" ht="19.5">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -11186,11 +10549,11 @@
       <c r="L73" s="10"/>
       <c r="M73" s="12"/>
       <c r="N73" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O73" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P73" s="12">
@@ -11201,30 +10564,26 @@
       <c r="R73" s="10"/>
       <c r="S73" s="12"/>
       <c r="T73" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U73" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V73" s="12"/>
+      <c r="W73" s="10"/>
+      <c r="X73" s="12"/>
+      <c r="Y73" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z73" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U73" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V73" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W73" s="12"/>
-      <c r="X73" s="10"/>
-      <c r="Y73" s="12"/>
-      <c r="Z73" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA73" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:27" ht="19.5">
+    </row>
+    <row r="74" spans="1:26" ht="19.5">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -11255,11 +10614,11 @@
       <c r="L74" s="10"/>
       <c r="M74" s="12"/>
       <c r="N74" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O74" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P74" s="12">
@@ -11270,30 +10629,26 @@
       <c r="R74" s="10"/>
       <c r="S74" s="12"/>
       <c r="T74" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U74" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V74" s="12"/>
+      <c r="W74" s="10"/>
+      <c r="X74" s="12"/>
+      <c r="Y74" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z74" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U74" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V74" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W74" s="12"/>
-      <c r="X74" s="10"/>
-      <c r="Y74" s="12"/>
-      <c r="Z74" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA74" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:27" ht="19.5">
+    </row>
+    <row r="75" spans="1:26" ht="19.5">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -11324,11 +10679,11 @@
       <c r="L75" s="10"/>
       <c r="M75" s="12"/>
       <c r="N75" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O75" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P75" s="12">
@@ -11339,30 +10694,26 @@
       <c r="R75" s="10"/>
       <c r="S75" s="12"/>
       <c r="T75" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U75" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V75" s="12"/>
+      <c r="W75" s="10"/>
+      <c r="X75" s="12"/>
+      <c r="Y75" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z75" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U75" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V75" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W75" s="12"/>
-      <c r="X75" s="10"/>
-      <c r="Y75" s="12"/>
-      <c r="Z75" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA75" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:27" ht="19.5">
+    </row>
+    <row r="76" spans="1:26" ht="19.5">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -11393,11 +10744,11 @@
       <c r="L76" s="10"/>
       <c r="M76" s="12"/>
       <c r="N76" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O76" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P76" s="12">
@@ -11408,30 +10759,26 @@
       <c r="R76" s="10"/>
       <c r="S76" s="12"/>
       <c r="T76" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U76" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V76" s="12"/>
+      <c r="W76" s="10"/>
+      <c r="X76" s="12"/>
+      <c r="Y76" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z76" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U76" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V76" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W76" s="12"/>
-      <c r="X76" s="10"/>
-      <c r="Y76" s="12"/>
-      <c r="Z76" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA76" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:27" ht="19.5">
+    </row>
+    <row r="77" spans="1:26" ht="19.5">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -11462,11 +10809,11 @@
       <c r="L77" s="10"/>
       <c r="M77" s="12"/>
       <c r="N77" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O77" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P77" s="12">
@@ -11477,30 +10824,26 @@
       <c r="R77" s="10"/>
       <c r="S77" s="12"/>
       <c r="T77" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U77" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V77" s="12"/>
+      <c r="W77" s="10"/>
+      <c r="X77" s="12"/>
+      <c r="Y77" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z77" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U77" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V77" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W77" s="12"/>
-      <c r="X77" s="10"/>
-      <c r="Y77" s="12"/>
-      <c r="Z77" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA77" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:27" ht="19.5">
+    </row>
+    <row r="78" spans="1:26" ht="19.5">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -11516,11 +10859,11 @@
       <c r="F78" s="10"/>
       <c r="G78" s="12"/>
       <c r="H78" s="12">
-        <f t="shared" ref="H78:H127" si="22">IF((D78-E78)&lt;0,0,(D78-E78))</f>
+        <f t="shared" ref="H78:H127" si="19">IF((D78-E78)&lt;0,0,(D78-E78))</f>
         <v>0</v>
       </c>
       <c r="I78" s="12">
-        <f t="shared" ref="I78:I127" si="23">IF((E78-D78)&lt;0,0,(E78-D78))</f>
+        <f t="shared" ref="I78:I127" si="20">IF((E78-D78)&lt;0,0,(E78-D78))</f>
         <v>0</v>
       </c>
       <c r="J78" s="12">
@@ -11531,11 +10874,11 @@
       <c r="L78" s="10"/>
       <c r="M78" s="12"/>
       <c r="N78" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O78" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P78" s="12">
@@ -11546,30 +10889,26 @@
       <c r="R78" s="10"/>
       <c r="S78" s="12"/>
       <c r="T78" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U78" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V78" s="12"/>
+      <c r="W78" s="10"/>
+      <c r="X78" s="12"/>
+      <c r="Y78" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z78" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U78" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V78" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W78" s="12"/>
-      <c r="X78" s="10"/>
-      <c r="Y78" s="12"/>
-      <c r="Z78" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA78" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:27" ht="19.5">
+    </row>
+    <row r="79" spans="1:26" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -11585,11 +10924,11 @@
       <c r="F79" s="10"/>
       <c r="G79" s="12"/>
       <c r="H79" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I79" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J79" s="12">
@@ -11600,11 +10939,11 @@
       <c r="L79" s="10"/>
       <c r="M79" s="12"/>
       <c r="N79" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O79" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P79" s="12">
@@ -11615,30 +10954,26 @@
       <c r="R79" s="10"/>
       <c r="S79" s="12"/>
       <c r="T79" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U79" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V79" s="12"/>
+      <c r="W79" s="10"/>
+      <c r="X79" s="12"/>
+      <c r="Y79" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z79" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U79" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V79" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W79" s="12"/>
-      <c r="X79" s="10"/>
-      <c r="Y79" s="12"/>
-      <c r="Z79" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA79" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:27" ht="19.5">
+    </row>
+    <row r="80" spans="1:26" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -11654,11 +10989,11 @@
       <c r="F80" s="10"/>
       <c r="G80" s="12"/>
       <c r="H80" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I80" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J80" s="12">
@@ -11669,11 +11004,11 @@
       <c r="L80" s="10"/>
       <c r="M80" s="12"/>
       <c r="N80" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O80" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P80" s="12">
@@ -11684,30 +11019,26 @@
       <c r="R80" s="10"/>
       <c r="S80" s="12"/>
       <c r="T80" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U80" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V80" s="12"/>
+      <c r="W80" s="10"/>
+      <c r="X80" s="12"/>
+      <c r="Y80" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z80" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U80" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V80" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W80" s="12"/>
-      <c r="X80" s="10"/>
-      <c r="Y80" s="12"/>
-      <c r="Z80" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA80" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:27" ht="19.5">
+    </row>
+    <row r="81" spans="1:26" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -11723,11 +11054,11 @@
       <c r="F81" s="10"/>
       <c r="G81" s="12"/>
       <c r="H81" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I81" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J81" s="12">
@@ -11738,11 +11069,11 @@
       <c r="L81" s="10"/>
       <c r="M81" s="12"/>
       <c r="N81" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O81" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P81" s="12">
@@ -11753,30 +11084,26 @@
       <c r="R81" s="10"/>
       <c r="S81" s="12"/>
       <c r="T81" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U81" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V81" s="12"/>
+      <c r="W81" s="10"/>
+      <c r="X81" s="12"/>
+      <c r="Y81" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z81" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U81" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V81" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W81" s="12"/>
-      <c r="X81" s="10"/>
-      <c r="Y81" s="12"/>
-      <c r="Z81" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA81" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    </row>
+    <row r="82" spans="1:26" s="7" customFormat="1" ht="19.5">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -11785,12 +11112,11 @@
       <c r="S82" s="5"/>
       <c r="T82" s="13"/>
       <c r="U82" s="13"/>
-      <c r="V82" s="13"/>
-      <c r="Y82" s="5"/>
+      <c r="X82" s="5"/>
+      <c r="Y82" s="13"/>
       <c r="Z82" s="13"/>
-      <c r="AA82" s="13"/>
-    </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    </row>
+    <row r="83" spans="1:26" ht="19.5">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -11806,11 +11132,11 @@
       <c r="F83" s="10"/>
       <c r="G83" s="12"/>
       <c r="H83" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I83" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J83" s="12">
@@ -11821,11 +11147,11 @@
       <c r="L83" s="10"/>
       <c r="M83" s="12"/>
       <c r="N83" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O83" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P83" s="12">
@@ -11836,30 +11162,26 @@
       <c r="R83" s="10"/>
       <c r="S83" s="12"/>
       <c r="T83" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U83" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V83" s="12"/>
+      <c r="W83" s="10"/>
+      <c r="X83" s="12"/>
+      <c r="Y83" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z83" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U83" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V83" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W83" s="12"/>
-      <c r="X83" s="10"/>
-      <c r="Y83" s="12"/>
-      <c r="Z83" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA83" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:27" ht="19.5">
+    </row>
+    <row r="84" spans="1:26" ht="19.5">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -11875,11 +11197,11 @@
       <c r="F84" s="10"/>
       <c r="G84" s="12"/>
       <c r="H84" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I84" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J84" s="12">
@@ -11890,11 +11212,11 @@
       <c r="L84" s="10"/>
       <c r="M84" s="12"/>
       <c r="N84" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O84" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P84" s="12">
@@ -11905,30 +11227,26 @@
       <c r="R84" s="10"/>
       <c r="S84" s="12"/>
       <c r="T84" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U84" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V84" s="12"/>
+      <c r="W84" s="10"/>
+      <c r="X84" s="12"/>
+      <c r="Y84" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z84" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U84" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V84" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W84" s="12"/>
-      <c r="X84" s="10"/>
-      <c r="Y84" s="12"/>
-      <c r="Z84" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA84" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:27" ht="19.5">
+    </row>
+    <row r="85" spans="1:26" ht="19.5">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -11944,11 +11262,11 @@
       <c r="F85" s="10"/>
       <c r="G85" s="12"/>
       <c r="H85" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I85" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J85" s="12">
@@ -11959,11 +11277,11 @@
       <c r="L85" s="10"/>
       <c r="M85" s="12"/>
       <c r="N85" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O85" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P85" s="12">
@@ -11974,30 +11292,26 @@
       <c r="R85" s="10"/>
       <c r="S85" s="12"/>
       <c r="T85" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U85" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V85" s="12"/>
+      <c r="W85" s="10"/>
+      <c r="X85" s="12"/>
+      <c r="Y85" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z85" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U85" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V85" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W85" s="12"/>
-      <c r="X85" s="10"/>
-      <c r="Y85" s="12"/>
-      <c r="Z85" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA85" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:27" ht="19.5">
+    </row>
+    <row r="86" spans="1:26" ht="19.5">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -12013,11 +11327,11 @@
       <c r="F86" s="10"/>
       <c r="G86" s="12"/>
       <c r="H86" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I86" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J86" s="12">
@@ -12028,11 +11342,11 @@
       <c r="L86" s="10"/>
       <c r="M86" s="12"/>
       <c r="N86" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O86" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P86" s="12">
@@ -12043,30 +11357,26 @@
       <c r="R86" s="10"/>
       <c r="S86" s="12"/>
       <c r="T86" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U86" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V86" s="12"/>
+      <c r="W86" s="10"/>
+      <c r="X86" s="12"/>
+      <c r="Y86" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z86" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U86" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V86" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W86" s="12"/>
-      <c r="X86" s="10"/>
-      <c r="Y86" s="12"/>
-      <c r="Z86" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA86" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:27" ht="19.5">
+    </row>
+    <row r="87" spans="1:26" ht="19.5">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -12082,11 +11392,11 @@
       <c r="F87" s="10"/>
       <c r="G87" s="12"/>
       <c r="H87" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I87" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J87" s="12">
@@ -12097,11 +11407,11 @@
       <c r="L87" s="10"/>
       <c r="M87" s="12"/>
       <c r="N87" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O87" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P87" s="12">
@@ -12112,30 +11422,26 @@
       <c r="R87" s="10"/>
       <c r="S87" s="12"/>
       <c r="T87" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U87" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V87" s="12"/>
+      <c r="W87" s="10"/>
+      <c r="X87" s="12"/>
+      <c r="Y87" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z87" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U87" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V87" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W87" s="12"/>
-      <c r="X87" s="10"/>
-      <c r="Y87" s="12"/>
-      <c r="Z87" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA87" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:27" ht="19.5">
+    </row>
+    <row r="88" spans="1:26" ht="19.5">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -12151,11 +11457,11 @@
       <c r="F88" s="10"/>
       <c r="G88" s="12"/>
       <c r="H88" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I88" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J88" s="12">
@@ -12166,11 +11472,11 @@
       <c r="L88" s="10"/>
       <c r="M88" s="12"/>
       <c r="N88" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O88" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P88" s="12">
@@ -12181,30 +11487,26 @@
       <c r="R88" s="10"/>
       <c r="S88" s="12"/>
       <c r="T88" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U88" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V88" s="12"/>
+      <c r="W88" s="10"/>
+      <c r="X88" s="12"/>
+      <c r="Y88" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z88" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U88" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V88" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W88" s="12"/>
-      <c r="X88" s="10"/>
-      <c r="Y88" s="12"/>
-      <c r="Z88" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA88" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:27" ht="19.5">
+    </row>
+    <row r="89" spans="1:26" ht="19.5">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -12220,11 +11522,11 @@
       <c r="F89" s="10"/>
       <c r="G89" s="12"/>
       <c r="H89" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I89" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J89" s="12">
@@ -12235,11 +11537,11 @@
       <c r="L89" s="10"/>
       <c r="M89" s="12"/>
       <c r="N89" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O89" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P89" s="12">
@@ -12250,30 +11552,26 @@
       <c r="R89" s="10"/>
       <c r="S89" s="12"/>
       <c r="T89" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U89" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V89" s="12"/>
+      <c r="W89" s="10"/>
+      <c r="X89" s="12"/>
+      <c r="Y89" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z89" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U89" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V89" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W89" s="12"/>
-      <c r="X89" s="10"/>
-      <c r="Y89" s="12"/>
-      <c r="Z89" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA89" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:27" ht="19.5">
+    </row>
+    <row r="90" spans="1:26" ht="19.5">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -12289,11 +11587,11 @@
       <c r="F90" s="10"/>
       <c r="G90" s="12"/>
       <c r="H90" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I90" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J90" s="12">
@@ -12304,11 +11602,11 @@
       <c r="L90" s="10"/>
       <c r="M90" s="12"/>
       <c r="N90" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O90" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P90" s="12">
@@ -12319,30 +11617,26 @@
       <c r="R90" s="10"/>
       <c r="S90" s="12"/>
       <c r="T90" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U90" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V90" s="12"/>
+      <c r="W90" s="10"/>
+      <c r="X90" s="12"/>
+      <c r="Y90" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z90" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U90" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V90" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W90" s="12"/>
-      <c r="X90" s="10"/>
-      <c r="Y90" s="12"/>
-      <c r="Z90" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA90" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:27" ht="19.5">
+    </row>
+    <row r="91" spans="1:26" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -12358,11 +11652,11 @@
       <c r="F91" s="10"/>
       <c r="G91" s="12"/>
       <c r="H91" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I91" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J91" s="12">
@@ -12373,11 +11667,11 @@
       <c r="L91" s="10"/>
       <c r="M91" s="12"/>
       <c r="N91" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O91" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P91" s="12">
@@ -12388,43 +11682,37 @@
       <c r="R91" s="10"/>
       <c r="S91" s="12"/>
       <c r="T91" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U91" s="12">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V91" s="12"/>
+      <c r="W91" s="10"/>
+      <c r="X91" s="12"/>
+      <c r="Y91" s="12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z91" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U91" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V91" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W91" s="12"/>
-      <c r="X91" s="10"/>
-      <c r="Y91" s="12"/>
-      <c r="Z91" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA91" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.5">
+    </row>
+    <row r="92" spans="1:26" s="7" customFormat="1" ht="19.5">
       <c r="J92" s="13"/>
       <c r="N92" s="13"/>
       <c r="O92" s="13"/>
       <c r="P92" s="13"/>
-      <c r="S92" s="5"/>
       <c r="T92" s="13"/>
       <c r="U92" s="13"/>
-      <c r="V92" s="13"/>
-      <c r="Y92" s="5"/>
+      <c r="X92" s="5"/>
+      <c r="Y92" s="13"/>
       <c r="Z92" s="13"/>
-      <c r="AA92" s="13"/>
-    </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    </row>
+    <row r="93" spans="1:26" ht="19.5">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -12474,26 +11762,22 @@
         <v>0</v>
       </c>
       <c r="U93" s="12">
-        <f>IF((Q93-P93)&lt;0,0,(Q93-P93))</f>
-        <v>0</v>
-      </c>
-      <c r="V93" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W93" s="12"/>
-      <c r="X93" s="10"/>
-      <c r="Y93" s="12"/>
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V93" s="12"/>
+      <c r="W93" s="10"/>
+      <c r="X93" s="12"/>
+      <c r="Y93" s="12">
+        <f>IF((U93-V93)&lt;0,0,(U93-V93))</f>
+        <v>0</v>
+      </c>
       <c r="Z93" s="12">
-        <f>IF((V93-W93)&lt;0,0,(V93-W93))</f>
-        <v>0</v>
-      </c>
-      <c r="AA93" s="12">
-        <f>IF((W93-V93)&lt;0,0,(W93-V93))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:27" ht="19.5">
+        <f>IF((V93-U93)&lt;0,0,(V93-U93))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:26" ht="19.5">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -12543,26 +11827,22 @@
         <v>0</v>
       </c>
       <c r="U94" s="12">
-        <f>IF((Q94-P94)&lt;0,0,(Q94-P94))</f>
-        <v>0</v>
-      </c>
-      <c r="V94" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W94" s="12"/>
-      <c r="X94" s="10"/>
-      <c r="Y94" s="12"/>
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V94" s="12"/>
+      <c r="W94" s="10"/>
+      <c r="X94" s="12"/>
+      <c r="Y94" s="12">
+        <f>IF((U94-V94)&lt;0,0,(U94-V94))</f>
+        <v>0</v>
+      </c>
       <c r="Z94" s="12">
-        <f>IF((V94-W94)&lt;0,0,(V94-W94))</f>
-        <v>0</v>
-      </c>
-      <c r="AA94" s="12">
-        <f>IF((W94-V94)&lt;0,0,(W94-V94))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:27" ht="19.5">
+        <f>IF((V94-U94)&lt;0,0,(V94-U94))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:26" ht="19.5">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -12612,26 +11892,22 @@
         <v>0</v>
       </c>
       <c r="U95" s="12">
-        <f>IF((Q95-P95)&lt;0,0,(Q95-P95))</f>
-        <v>0</v>
-      </c>
-      <c r="V95" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W95" s="12"/>
-      <c r="X95" s="10"/>
-      <c r="Y95" s="12"/>
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V95" s="12"/>
+      <c r="W95" s="10"/>
+      <c r="X95" s="12"/>
+      <c r="Y95" s="12">
+        <f>IF((U95-V95)&lt;0,0,(U95-V95))</f>
+        <v>0</v>
+      </c>
       <c r="Z95" s="12">
-        <f>IF((V95-W95)&lt;0,0,(V95-W95))</f>
-        <v>0</v>
-      </c>
-      <c r="AA95" s="12">
-        <f>IF((W95-V95)&lt;0,0,(W95-V95))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:27" ht="19.5">
+        <f>IF((V95-U95)&lt;0,0,(V95-U95))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:26" ht="19.5">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -12681,26 +11957,22 @@
         <v>0</v>
       </c>
       <c r="U96" s="12">
-        <f>IF((Q96-P96)&lt;0,0,(Q96-P96))</f>
-        <v>0</v>
-      </c>
-      <c r="V96" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W96" s="12"/>
-      <c r="X96" s="10"/>
-      <c r="Y96" s="12"/>
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V96" s="12"/>
+      <c r="W96" s="10"/>
+      <c r="X96" s="12"/>
+      <c r="Y96" s="12">
+        <f>IF((U96-V96)&lt;0,0,(U96-V96))</f>
+        <v>0</v>
+      </c>
       <c r="Z96" s="12">
-        <f>IF((V96-W96)&lt;0,0,(V96-W96))</f>
-        <v>0</v>
-      </c>
-      <c r="AA96" s="12">
-        <f>IF((W96-V96)&lt;0,0,(W96-V96))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:27" ht="19.5">
+        <f>IF((V96-U96)&lt;0,0,(V96-U96))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:26" ht="19.5">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -12750,26 +12022,22 @@
         <v>0</v>
       </c>
       <c r="U97" s="12">
-        <f>IF((Q97-P97)&lt;0,0,(Q97-P97))</f>
-        <v>0</v>
-      </c>
-      <c r="V97" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W97" s="12"/>
-      <c r="X97" s="10"/>
-      <c r="Y97" s="12"/>
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V97" s="12"/>
+      <c r="W97" s="10"/>
+      <c r="X97" s="12"/>
+      <c r="Y97" s="12">
+        <f>IF((U97-V97)&lt;0,0,(U97-V97))</f>
+        <v>0</v>
+      </c>
       <c r="Z97" s="12">
-        <f>IF((V97-W97)&lt;0,0,(V97-W97))</f>
-        <v>0</v>
-      </c>
-      <c r="AA97" s="12">
-        <f>IF((W97-V97)&lt;0,0,(W97-V97))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:27" ht="19.5">
+        <f>IF((V97-U97)&lt;0,0,(V97-U97))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:26" ht="19.5">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -12819,26 +12087,22 @@
         <v>0</v>
       </c>
       <c r="U98" s="12">
-        <f>IF((Q98-P98)&lt;0,0,(Q98-P98))</f>
-        <v>0</v>
-      </c>
-      <c r="V98" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W98" s="12"/>
-      <c r="X98" s="10"/>
-      <c r="Y98" s="12"/>
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V98" s="12"/>
+      <c r="W98" s="10"/>
+      <c r="X98" s="12"/>
+      <c r="Y98" s="12">
+        <f>IF((U98-V98)&lt;0,0,(U98-V98))</f>
+        <v>0</v>
+      </c>
       <c r="Z98" s="12">
-        <f>IF((V98-W98)&lt;0,0,(V98-W98))</f>
-        <v>0</v>
-      </c>
-      <c r="AA98" s="12">
-        <f>IF((W98-V98)&lt;0,0,(W98-V98))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:27" ht="19.5">
+        <f>IF((V98-U98)&lt;0,0,(V98-U98))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:26" ht="19.5">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -12888,26 +12152,22 @@
         <v>0</v>
       </c>
       <c r="U99" s="12">
-        <f>IF((Q99-P99)&lt;0,0,(Q99-P99))</f>
-        <v>0</v>
-      </c>
-      <c r="V99" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W99" s="12"/>
-      <c r="X99" s="10"/>
-      <c r="Y99" s="12"/>
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V99" s="12"/>
+      <c r="W99" s="10"/>
+      <c r="X99" s="12"/>
+      <c r="Y99" s="12">
+        <f>IF((U99-V99)&lt;0,0,(U99-V99))</f>
+        <v>0</v>
+      </c>
       <c r="Z99" s="12">
-        <f>IF((V99-W99)&lt;0,0,(V99-W99))</f>
-        <v>0</v>
-      </c>
-      <c r="AA99" s="12">
-        <f>IF((W99-V99)&lt;0,0,(W99-V99))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:27" ht="19.5">
+        <f>IF((V99-U99)&lt;0,0,(V99-U99))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:26" ht="19.5">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -12957,26 +12217,22 @@
         <v>0</v>
       </c>
       <c r="U100" s="12">
-        <f>IF((Q100-P100)&lt;0,0,(Q100-P100))</f>
-        <v>0</v>
-      </c>
-      <c r="V100" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W100" s="12"/>
-      <c r="X100" s="10"/>
-      <c r="Y100" s="12"/>
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V100" s="12"/>
+      <c r="W100" s="10"/>
+      <c r="X100" s="12"/>
+      <c r="Y100" s="12">
+        <f>IF((U100-V100)&lt;0,0,(U100-V100))</f>
+        <v>0</v>
+      </c>
       <c r="Z100" s="12">
-        <f>IF((V100-W100)&lt;0,0,(V100-W100))</f>
-        <v>0</v>
-      </c>
-      <c r="AA100" s="12">
-        <f>IF((W100-V100)&lt;0,0,(W100-V100))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:27" ht="19.5">
+        <f>IF((V100-U100)&lt;0,0,(V100-U100))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:26" ht="19.5">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -13026,26 +12282,22 @@
         <v>0</v>
       </c>
       <c r="U101" s="12">
-        <f>IF((Q101-P101)&lt;0,0,(Q101-P101))</f>
-        <v>0</v>
-      </c>
-      <c r="V101" s="12">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W101" s="12"/>
-      <c r="X101" s="10"/>
-      <c r="Y101" s="12"/>
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V101" s="12"/>
+      <c r="W101" s="10"/>
+      <c r="X101" s="12"/>
+      <c r="Y101" s="12">
+        <f>IF((U101-V101)&lt;0,0,(U101-V101))</f>
+        <v>0</v>
+      </c>
       <c r="Z101" s="12">
-        <f>IF((V101-W101)&lt;0,0,(V101-W101))</f>
-        <v>0</v>
-      </c>
-      <c r="AA101" s="12">
-        <f>IF((W101-V101)&lt;0,0,(W101-V101))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+        <f>IF((V101-U101)&lt;0,0,(V101-U101))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:26" s="7" customFormat="1" ht="19.5">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -13054,12 +12306,11 @@
       <c r="S102" s="5"/>
       <c r="T102" s="13"/>
       <c r="U102" s="13"/>
-      <c r="V102" s="13"/>
-      <c r="Y102" s="5"/>
+      <c r="X102" s="5"/>
+      <c r="Y102" s="13"/>
       <c r="Z102" s="13"/>
-      <c r="AA102" s="13"/>
-    </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    </row>
+    <row r="103" spans="1:26" ht="38.25">
       <c r="A103" s="1" t="s">
         <v>26</v>
       </c>
@@ -13075,11 +12326,11 @@
       <c r="F103" s="1"/>
       <c r="G103" s="5"/>
       <c r="H103" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I103" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J103" s="5">
@@ -13090,11 +12341,11 @@
       <c r="L103" s="1"/>
       <c r="M103" s="5"/>
       <c r="N103" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O103" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P103" s="5">
@@ -13105,30 +12356,26 @@
       <c r="R103" s="1"/>
       <c r="S103" s="5"/>
       <c r="T103" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U103" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V103" s="5"/>
+      <c r="W103" s="1"/>
+      <c r="X103" s="5"/>
+      <c r="Y103" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z103" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U103" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V103" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W103" s="5"/>
-      <c r="X103" s="1"/>
-      <c r="Y103" s="5"/>
-      <c r="Z103" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA103" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:27" ht="19.5">
+    </row>
+    <row r="104" spans="1:26" ht="19.5">
       <c r="A104" s="1" t="s">
         <v>26</v>
       </c>
@@ -13144,11 +12391,11 @@
       <c r="F104" s="1"/>
       <c r="G104" s="5"/>
       <c r="H104" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I104" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J104" s="5">
@@ -13159,11 +12406,11 @@
       <c r="L104" s="1"/>
       <c r="M104" s="5"/>
       <c r="N104" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O104" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P104" s="5">
@@ -13174,30 +12421,26 @@
       <c r="R104" s="1"/>
       <c r="S104" s="5"/>
       <c r="T104" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U104" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V104" s="5"/>
+      <c r="W104" s="1"/>
+      <c r="X104" s="5"/>
+      <c r="Y104" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z104" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U104" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V104" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W104" s="5"/>
-      <c r="X104" s="1"/>
-      <c r="Y104" s="5"/>
-      <c r="Z104" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA104" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:27" ht="19.5">
+    </row>
+    <row r="105" spans="1:26" ht="19.5">
       <c r="A105" s="1" t="s">
         <v>26</v>
       </c>
@@ -13213,11 +12456,11 @@
       <c r="F105" s="1"/>
       <c r="G105" s="5"/>
       <c r="H105" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I105" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J105" s="5">
@@ -13228,11 +12471,11 @@
       <c r="L105" s="1"/>
       <c r="M105" s="5"/>
       <c r="N105" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O105" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P105" s="5">
@@ -13243,30 +12486,26 @@
       <c r="R105" s="1"/>
       <c r="S105" s="5"/>
       <c r="T105" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U105" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V105" s="5"/>
+      <c r="W105" s="1"/>
+      <c r="X105" s="5"/>
+      <c r="Y105" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z105" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U105" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V105" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W105" s="5"/>
-      <c r="X105" s="1"/>
-      <c r="Y105" s="5"/>
-      <c r="Z105" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA105" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:27" ht="19.5">
+    </row>
+    <row r="106" spans="1:26" ht="19.5">
       <c r="A106" s="1" t="s">
         <v>26</v>
       </c>
@@ -13282,11 +12521,11 @@
       <c r="F106" s="1"/>
       <c r="G106" s="5"/>
       <c r="H106" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I106" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J106" s="5">
@@ -13297,11 +12536,11 @@
       <c r="L106" s="1"/>
       <c r="M106" s="5"/>
       <c r="N106" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O106" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P106" s="5">
@@ -13312,30 +12551,26 @@
       <c r="R106" s="1"/>
       <c r="S106" s="5"/>
       <c r="T106" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U106" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V106" s="5"/>
+      <c r="W106" s="1"/>
+      <c r="X106" s="5"/>
+      <c r="Y106" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z106" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U106" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V106" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W106" s="5"/>
-      <c r="X106" s="1"/>
-      <c r="Y106" s="5"/>
-      <c r="Z106" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA106" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:27" ht="38.25">
+    </row>
+    <row r="107" spans="1:26" ht="38.25">
       <c r="A107" s="1" t="s">
         <v>26</v>
       </c>
@@ -13351,11 +12586,11 @@
       <c r="F107" s="1"/>
       <c r="G107" s="5"/>
       <c r="H107" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I107" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J107" s="5">
@@ -13366,11 +12601,11 @@
       <c r="L107" s="1"/>
       <c r="M107" s="5"/>
       <c r="N107" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O107" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P107" s="5">
@@ -13381,30 +12616,26 @@
       <c r="R107" s="1"/>
       <c r="S107" s="5"/>
       <c r="T107" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U107" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V107" s="5"/>
+      <c r="W107" s="1"/>
+      <c r="X107" s="5"/>
+      <c r="Y107" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z107" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U107" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V107" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W107" s="5"/>
-      <c r="X107" s="1"/>
-      <c r="Y107" s="5"/>
-      <c r="Z107" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA107" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:27" ht="38.25">
+    </row>
+    <row r="108" spans="1:26" ht="38.25">
       <c r="A108" s="1" t="s">
         <v>26</v>
       </c>
@@ -13420,11 +12651,11 @@
       <c r="F108" s="1"/>
       <c r="G108" s="5"/>
       <c r="H108" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I108" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J108" s="5">
@@ -13435,11 +12666,11 @@
       <c r="L108" s="1"/>
       <c r="M108" s="5"/>
       <c r="N108" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O108" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P108" s="5">
@@ -13450,30 +12681,26 @@
       <c r="R108" s="1"/>
       <c r="S108" s="5"/>
       <c r="T108" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U108" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V108" s="5"/>
+      <c r="W108" s="1"/>
+      <c r="X108" s="5"/>
+      <c r="Y108" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z108" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U108" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V108" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W108" s="5"/>
-      <c r="X108" s="1"/>
-      <c r="Y108" s="5"/>
-      <c r="Z108" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA108" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:27" ht="57.75">
+    </row>
+    <row r="109" spans="1:26" ht="57.75">
       <c r="A109" s="1" t="s">
         <v>26</v>
       </c>
@@ -13489,11 +12716,11 @@
       <c r="F109" s="1"/>
       <c r="G109" s="5"/>
       <c r="H109" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I109" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J109" s="5">
@@ -13504,11 +12731,11 @@
       <c r="L109" s="1"/>
       <c r="M109" s="5"/>
       <c r="N109" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O109" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P109" s="5">
@@ -13519,30 +12746,26 @@
       <c r="R109" s="1"/>
       <c r="S109" s="5"/>
       <c r="T109" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U109" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V109" s="5"/>
+      <c r="W109" s="1"/>
+      <c r="X109" s="5"/>
+      <c r="Y109" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z109" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U109" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V109" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W109" s="5"/>
-      <c r="X109" s="1"/>
-      <c r="Y109" s="5"/>
-      <c r="Z109" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA109" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:27" ht="38.25">
+    </row>
+    <row r="110" spans="1:26" ht="38.25">
       <c r="A110" s="1" t="s">
         <v>26</v>
       </c>
@@ -13558,11 +12781,11 @@
       <c r="F110" s="1"/>
       <c r="G110" s="5"/>
       <c r="H110" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I110" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J110" s="5">
@@ -13573,11 +12796,11 @@
       <c r="L110" s="1"/>
       <c r="M110" s="5"/>
       <c r="N110" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O110" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P110" s="5">
@@ -13588,41 +12811,36 @@
       <c r="R110" s="1"/>
       <c r="S110" s="5"/>
       <c r="T110" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U110" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V110" s="5"/>
+      <c r="W110" s="1"/>
+      <c r="X110" s="5"/>
+      <c r="Y110" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z110" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U110" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V110" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W110" s="5"/>
-      <c r="X110" s="1"/>
-      <c r="Y110" s="5"/>
-      <c r="Z110" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA110" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    </row>
+    <row r="111" spans="1:26" s="7" customFormat="1" ht="19.5">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
       <c r="P111" s="13"/>
       <c r="T111" s="13"/>
       <c r="U111" s="13"/>
-      <c r="V111" s="13"/>
+      <c r="Y111" s="13"/>
       <c r="Z111" s="13"/>
-      <c r="AA111" s="13"/>
-    </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    </row>
+    <row r="112" spans="1:26" ht="19.5">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -13631,11 +12849,11 @@
       <c r="F112" s="1"/>
       <c r="G112" s="5"/>
       <c r="H112" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I112" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J112" s="5">
@@ -13646,11 +12864,11 @@
       <c r="L112" s="1"/>
       <c r="M112" s="5"/>
       <c r="N112" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O112" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P112" s="5">
@@ -13661,30 +12879,26 @@
       <c r="R112" s="1"/>
       <c r="S112" s="5"/>
       <c r="T112" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U112" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V112" s="5"/>
+      <c r="W112" s="1"/>
+      <c r="X112" s="5"/>
+      <c r="Y112" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z112" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U112" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V112" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W112" s="5"/>
-      <c r="X112" s="1"/>
-      <c r="Y112" s="5"/>
-      <c r="Z112" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA112" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:27" ht="19.5">
+    </row>
+    <row r="113" spans="1:26" ht="19.5">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -13693,11 +12907,11 @@
       <c r="F113" s="1"/>
       <c r="G113" s="5"/>
       <c r="H113" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I113" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J113" s="5">
@@ -13708,11 +12922,11 @@
       <c r="L113" s="1"/>
       <c r="M113" s="5"/>
       <c r="N113" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O113" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P113" s="5">
@@ -13723,30 +12937,26 @@
       <c r="R113" s="1"/>
       <c r="S113" s="5"/>
       <c r="T113" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U113" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V113" s="5"/>
+      <c r="W113" s="1"/>
+      <c r="X113" s="5"/>
+      <c r="Y113" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z113" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U113" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V113" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W113" s="5"/>
-      <c r="X113" s="1"/>
-      <c r="Y113" s="5"/>
-      <c r="Z113" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA113" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:27" ht="19.5">
+    </row>
+    <row r="114" spans="1:26" ht="19.5">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -13755,11 +12965,11 @@
       <c r="F114" s="1"/>
       <c r="G114" s="5"/>
       <c r="H114" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I114" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J114" s="5">
@@ -13770,11 +12980,11 @@
       <c r="L114" s="1"/>
       <c r="M114" s="5"/>
       <c r="N114" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O114" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P114" s="5">
@@ -13785,30 +12995,26 @@
       <c r="R114" s="1"/>
       <c r="S114" s="5"/>
       <c r="T114" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U114" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V114" s="5"/>
+      <c r="W114" s="1"/>
+      <c r="X114" s="5"/>
+      <c r="Y114" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z114" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U114" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V114" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W114" s="5"/>
-      <c r="X114" s="1"/>
-      <c r="Y114" s="5"/>
-      <c r="Z114" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA114" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:27" ht="19.5">
+    </row>
+    <row r="115" spans="1:26" ht="19.5">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -13817,11 +13023,11 @@
       <c r="F115" s="1"/>
       <c r="G115" s="5"/>
       <c r="H115" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I115" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J115" s="5">
@@ -13832,11 +13038,11 @@
       <c r="L115" s="1"/>
       <c r="M115" s="5"/>
       <c r="N115" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O115" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P115" s="5">
@@ -13847,30 +13053,26 @@
       <c r="R115" s="1"/>
       <c r="S115" s="5"/>
       <c r="T115" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U115" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V115" s="5"/>
+      <c r="W115" s="1"/>
+      <c r="X115" s="5"/>
+      <c r="Y115" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z115" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U115" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V115" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W115" s="5"/>
-      <c r="X115" s="1"/>
-      <c r="Y115" s="5"/>
-      <c r="Z115" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA115" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:27" ht="19.5">
+    </row>
+    <row r="116" spans="1:26" ht="19.5">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -13879,11 +13081,11 @@
       <c r="F116" s="1"/>
       <c r="G116" s="5"/>
       <c r="H116" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I116" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J116" s="5">
@@ -13894,11 +13096,11 @@
       <c r="L116" s="1"/>
       <c r="M116" s="5"/>
       <c r="N116" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O116" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P116" s="5">
@@ -13909,30 +13111,26 @@
       <c r="R116" s="1"/>
       <c r="S116" s="5"/>
       <c r="T116" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U116" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V116" s="5"/>
+      <c r="W116" s="1"/>
+      <c r="X116" s="5"/>
+      <c r="Y116" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z116" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U116" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V116" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W116" s="5"/>
-      <c r="X116" s="1"/>
-      <c r="Y116" s="5"/>
-      <c r="Z116" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA116" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:27" ht="19.5">
+    </row>
+    <row r="117" spans="1:26" ht="19.5">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -13941,11 +13139,11 @@
       <c r="F117" s="1"/>
       <c r="G117" s="5"/>
       <c r="H117" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I117" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J117" s="5">
@@ -13956,11 +13154,11 @@
       <c r="L117" s="1"/>
       <c r="M117" s="5"/>
       <c r="N117" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O117" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P117" s="5">
@@ -13971,30 +13169,26 @@
       <c r="R117" s="1"/>
       <c r="S117" s="5"/>
       <c r="T117" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U117" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V117" s="5"/>
+      <c r="W117" s="1"/>
+      <c r="X117" s="5"/>
+      <c r="Y117" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z117" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U117" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V117" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W117" s="5"/>
-      <c r="X117" s="1"/>
-      <c r="Y117" s="5"/>
-      <c r="Z117" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA117" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:27" ht="19.5">
+    </row>
+    <row r="118" spans="1:26" ht="19.5">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -14003,11 +13197,11 @@
       <c r="F118" s="1"/>
       <c r="G118" s="5"/>
       <c r="H118" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I118" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J118" s="5">
@@ -14018,11 +13212,11 @@
       <c r="L118" s="1"/>
       <c r="M118" s="5"/>
       <c r="N118" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O118" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P118" s="5">
@@ -14033,30 +13227,26 @@
       <c r="R118" s="1"/>
       <c r="S118" s="5"/>
       <c r="T118" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U118" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V118" s="5"/>
+      <c r="W118" s="1"/>
+      <c r="X118" s="5"/>
+      <c r="Y118" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z118" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U118" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V118" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W118" s="5"/>
-      <c r="X118" s="1"/>
-      <c r="Y118" s="5"/>
-      <c r="Z118" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA118" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:27" ht="19.5">
+    </row>
+    <row r="119" spans="1:26" ht="19.5">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -14065,11 +13255,11 @@
       <c r="F119" s="1"/>
       <c r="G119" s="5"/>
       <c r="H119" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I119" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J119" s="5">
@@ -14080,11 +13270,11 @@
       <c r="L119" s="1"/>
       <c r="M119" s="5"/>
       <c r="N119" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O119" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P119" s="5">
@@ -14095,30 +13285,26 @@
       <c r="R119" s="1"/>
       <c r="S119" s="5"/>
       <c r="T119" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U119" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V119" s="5"/>
+      <c r="W119" s="1"/>
+      <c r="X119" s="5"/>
+      <c r="Y119" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z119" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U119" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V119" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W119" s="5"/>
-      <c r="X119" s="1"/>
-      <c r="Y119" s="5"/>
-      <c r="Z119" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA119" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:27" ht="19.5">
+    </row>
+    <row r="120" spans="1:26" ht="19.5">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -14127,11 +13313,11 @@
       <c r="F120" s="1"/>
       <c r="G120" s="5"/>
       <c r="H120" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I120" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J120" s="5">
@@ -14142,11 +13328,11 @@
       <c r="L120" s="1"/>
       <c r="M120" s="5"/>
       <c r="N120" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O120" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P120" s="5">
@@ -14157,30 +13343,26 @@
       <c r="R120" s="1"/>
       <c r="S120" s="5"/>
       <c r="T120" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U120" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V120" s="5"/>
+      <c r="W120" s="1"/>
+      <c r="X120" s="5"/>
+      <c r="Y120" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z120" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U120" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V120" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W120" s="5"/>
-      <c r="X120" s="1"/>
-      <c r="Y120" s="5"/>
-      <c r="Z120" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA120" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:27" ht="19.5">
+    </row>
+    <row r="121" spans="1:26" ht="19.5">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -14189,11 +13371,11 @@
       <c r="F121" s="1"/>
       <c r="G121" s="5"/>
       <c r="H121" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I121" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J121" s="5">
@@ -14204,11 +13386,11 @@
       <c r="L121" s="1"/>
       <c r="M121" s="5"/>
       <c r="N121" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O121" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P121" s="5">
@@ -14219,30 +13401,26 @@
       <c r="R121" s="1"/>
       <c r="S121" s="5"/>
       <c r="T121" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U121" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V121" s="5"/>
+      <c r="W121" s="1"/>
+      <c r="X121" s="5"/>
+      <c r="Y121" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z121" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U121" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V121" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W121" s="5"/>
-      <c r="X121" s="1"/>
-      <c r="Y121" s="5"/>
-      <c r="Z121" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA121" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:27" ht="19.5">
+    </row>
+    <row r="122" spans="1:26" ht="19.5">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -14251,11 +13429,11 @@
       <c r="F122" s="1"/>
       <c r="G122" s="5"/>
       <c r="H122" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I122" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J122" s="5">
@@ -14266,11 +13444,11 @@
       <c r="L122" s="1"/>
       <c r="M122" s="5"/>
       <c r="N122" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O122" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P122" s="5">
@@ -14281,30 +13459,26 @@
       <c r="R122" s="1"/>
       <c r="S122" s="5"/>
       <c r="T122" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U122" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V122" s="5"/>
+      <c r="W122" s="1"/>
+      <c r="X122" s="5"/>
+      <c r="Y122" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z122" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U122" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V122" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W122" s="5"/>
-      <c r="X122" s="1"/>
-      <c r="Y122" s="5"/>
-      <c r="Z122" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA122" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:27" ht="19.5">
+    </row>
+    <row r="123" spans="1:26" ht="19.5">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -14313,11 +13487,11 @@
       <c r="F123" s="1"/>
       <c r="G123" s="5"/>
       <c r="H123" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I123" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J123" s="5">
@@ -14328,11 +13502,11 @@
       <c r="L123" s="1"/>
       <c r="M123" s="5"/>
       <c r="N123" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O123" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P123" s="5">
@@ -14343,30 +13517,26 @@
       <c r="R123" s="1"/>
       <c r="S123" s="5"/>
       <c r="T123" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U123" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V123" s="5"/>
+      <c r="W123" s="1"/>
+      <c r="X123" s="5"/>
+      <c r="Y123" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z123" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U123" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V123" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W123" s="5"/>
-      <c r="X123" s="1"/>
-      <c r="Y123" s="5"/>
-      <c r="Z123" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA123" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:27" ht="19.5">
+    </row>
+    <row r="124" spans="1:26" ht="19.5">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -14375,11 +13545,11 @@
       <c r="F124" s="1"/>
       <c r="G124" s="5"/>
       <c r="H124" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I124" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J124" s="5">
@@ -14390,11 +13560,11 @@
       <c r="L124" s="1"/>
       <c r="M124" s="5"/>
       <c r="N124" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O124" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P124" s="5">
@@ -14405,30 +13575,26 @@
       <c r="R124" s="1"/>
       <c r="S124" s="5"/>
       <c r="T124" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U124" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V124" s="5"/>
+      <c r="W124" s="1"/>
+      <c r="X124" s="5"/>
+      <c r="Y124" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z124" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U124" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V124" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W124" s="5"/>
-      <c r="X124" s="1"/>
-      <c r="Y124" s="5"/>
-      <c r="Z124" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA124" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:27" ht="19.5">
+    </row>
+    <row r="125" spans="1:26" ht="19.5">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -14437,11 +13603,11 @@
       <c r="F125" s="1"/>
       <c r="G125" s="5"/>
       <c r="H125" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I125" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J125" s="5">
@@ -14452,11 +13618,11 @@
       <c r="L125" s="1"/>
       <c r="M125" s="5"/>
       <c r="N125" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O125" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P125" s="5">
@@ -14467,30 +13633,26 @@
       <c r="R125" s="1"/>
       <c r="S125" s="5"/>
       <c r="T125" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U125" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V125" s="5"/>
+      <c r="W125" s="1"/>
+      <c r="X125" s="5"/>
+      <c r="Y125" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z125" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U125" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V125" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W125" s="5"/>
-      <c r="X125" s="1"/>
-      <c r="Y125" s="5"/>
-      <c r="Z125" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA125" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:27" ht="19.5">
+    </row>
+    <row r="126" spans="1:26" ht="19.5">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -14499,11 +13661,11 @@
       <c r="F126" s="1"/>
       <c r="G126" s="5"/>
       <c r="H126" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I126" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J126" s="5">
@@ -14514,11 +13676,11 @@
       <c r="L126" s="1"/>
       <c r="M126" s="5"/>
       <c r="N126" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O126" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P126" s="5">
@@ -14529,30 +13691,26 @@
       <c r="R126" s="1"/>
       <c r="S126" s="5"/>
       <c r="T126" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U126" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V126" s="5"/>
+      <c r="W126" s="1"/>
+      <c r="X126" s="5"/>
+      <c r="Y126" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z126" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U126" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V126" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W126" s="5"/>
-      <c r="X126" s="1"/>
-      <c r="Y126" s="5"/>
-      <c r="Z126" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA126" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:27" ht="19.5">
+    </row>
+    <row r="127" spans="1:26" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -14561,11 +13719,11 @@
       <c r="F127" s="1"/>
       <c r="G127" s="31"/>
       <c r="H127" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I127" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J127" s="5">
@@ -14576,46 +13734,458 @@
       <c r="L127" s="1"/>
       <c r="M127" s="31"/>
       <c r="N127" s="5">
-        <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
+        <f t="shared" ref="N127" si="21">IF((J127-K127)&lt;0,0,(J127-K127))</f>
         <v>0</v>
       </c>
       <c r="O127" s="5">
-        <f t="shared" ref="O127" si="25">IF((K127-J127)&lt;0,0,(K127-J127))</f>
+        <f t="shared" ref="O127" si="22">IF((K127-J127)&lt;0,0,(K127-J127))</f>
         <v>0</v>
       </c>
       <c r="P127" s="5"/>
       <c r="Q127" s="31"/>
-      <c r="R127" s="29"/>
+      <c r="R127" s="1"/>
       <c r="S127" s="31"/>
       <c r="T127" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U127" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V127" s="31"/>
+      <c r="W127" s="1"/>
+      <c r="X127" s="31"/>
+      <c r="Y127" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z127" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U127" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V127" s="5">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W127" s="31"/>
-      <c r="X127" s="29"/>
-      <c r="Y127" s="31"/>
-      <c r="Z127" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA127" s="5">
-        <f t="shared" si="21"/>
+    </row>
+    <row r="128" spans="1:26" ht="19.5">
+      <c r="A128" s="32"/>
+      <c r="B128" s="33"/>
+      <c r="C128" s="32"/>
+      <c r="D128" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E128" s="34"/>
+      <c r="F128" s="32"/>
+      <c r="G128" s="34"/>
+      <c r="H128" s="34">
+        <f t="shared" ref="H128:H133" si="23">IF((D128-E128)&lt;0,0,(D128-E128))</f>
+        <v>0</v>
+      </c>
+      <c r="I128" s="34">
+        <f t="shared" ref="I128:I133" si="24">IF((E128-D128)&lt;0,0,(E128-D128))</f>
+        <v>0</v>
+      </c>
+      <c r="J128" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K128" s="34"/>
+      <c r="L128" s="32"/>
+      <c r="M128" s="34"/>
+      <c r="N128" s="34"/>
+      <c r="O128" s="34"/>
+      <c r="P128" s="34" t="e">
+        <f>#REF!*8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q128" s="34"/>
+      <c r="R128" s="32"/>
+      <c r="S128" s="34"/>
+      <c r="T128" s="34"/>
+      <c r="U128" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V128" s="34"/>
+      <c r="W128" s="1"/>
+      <c r="X128" s="34"/>
+      <c r="Y128" s="34">
+        <f t="shared" ref="Y128:Y133" si="25">IF((U128-V128)&lt;0,0,(U128-V128))</f>
+        <v>0</v>
+      </c>
+      <c r="Z128" s="34">
+        <f t="shared" ref="Z128:Z133" si="26">IF((V128-U128)&lt;0,0,(V128-U128))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:26" ht="19.5">
+      <c r="A129" s="32"/>
+      <c r="B129" s="33"/>
+      <c r="C129" s="32"/>
+      <c r="D129" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E129" s="34"/>
+      <c r="F129" s="32"/>
+      <c r="G129" s="34"/>
+      <c r="H129" s="34">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I129" s="34">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="J129" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K129" s="34"/>
+      <c r="L129" s="32"/>
+      <c r="M129" s="34"/>
+      <c r="N129" s="34"/>
+      <c r="O129" s="34"/>
+      <c r="P129" s="34" t="e">
+        <f>#REF!*8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q129" s="34"/>
+      <c r="R129" s="32"/>
+      <c r="S129" s="34"/>
+      <c r="T129" s="34"/>
+      <c r="U129" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V129" s="34"/>
+      <c r="W129" s="1"/>
+      <c r="X129" s="34"/>
+      <c r="Y129" s="34">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="Z129" s="34">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:26" ht="19.5">
+      <c r="A130" s="32"/>
+      <c r="B130" s="33"/>
+      <c r="C130" s="32"/>
+      <c r="D130" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E130" s="34"/>
+      <c r="F130" s="32"/>
+      <c r="G130" s="34"/>
+      <c r="H130" s="34">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I130" s="34">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="J130" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K130" s="34"/>
+      <c r="L130" s="32"/>
+      <c r="M130" s="34"/>
+      <c r="N130" s="34"/>
+      <c r="O130" s="34"/>
+      <c r="P130" s="34" t="e">
+        <f>#REF!*8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q130" s="34"/>
+      <c r="R130" s="32"/>
+      <c r="S130" s="34"/>
+      <c r="T130" s="34"/>
+      <c r="U130" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V130" s="34"/>
+      <c r="W130" s="1"/>
+      <c r="X130" s="34"/>
+      <c r="Y130" s="34">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="Z130" s="34">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:26" ht="19.5">
+      <c r="A131" s="32"/>
+      <c r="B131" s="33"/>
+      <c r="C131" s="32"/>
+      <c r="D131" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E131" s="34"/>
+      <c r="F131" s="32"/>
+      <c r="G131" s="34"/>
+      <c r="H131" s="34">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I131" s="34">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="J131" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K131" s="34"/>
+      <c r="L131" s="32"/>
+      <c r="M131" s="34"/>
+      <c r="N131" s="34"/>
+      <c r="O131" s="34"/>
+      <c r="P131" s="34" t="e">
+        <f>#REF!*8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q131" s="34"/>
+      <c r="R131" s="32"/>
+      <c r="S131" s="34"/>
+      <c r="T131" s="34"/>
+      <c r="U131" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V131" s="34"/>
+      <c r="W131" s="1"/>
+      <c r="X131" s="34"/>
+      <c r="Y131" s="34">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="Z131" s="34">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:26" ht="19.5">
+      <c r="A132" s="32"/>
+      <c r="B132" s="33"/>
+      <c r="C132" s="32"/>
+      <c r="D132" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E132" s="34"/>
+      <c r="F132" s="32"/>
+      <c r="G132" s="34"/>
+      <c r="H132" s="34">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I132" s="34">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="J132" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K132" s="34"/>
+      <c r="L132" s="32"/>
+      <c r="M132" s="34"/>
+      <c r="N132" s="34"/>
+      <c r="O132" s="34"/>
+      <c r="P132" s="34" t="e">
+        <f>#REF!*8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q132" s="34"/>
+      <c r="R132" s="32"/>
+      <c r="S132" s="34"/>
+      <c r="T132" s="34"/>
+      <c r="U132" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V132" s="34"/>
+      <c r="W132" s="1"/>
+      <c r="X132" s="34"/>
+      <c r="Y132" s="34">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="Z132" s="34">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:26" ht="19.5">
+      <c r="A133" s="32"/>
+      <c r="B133" s="33"/>
+      <c r="C133" s="32"/>
+      <c r="D133" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E133" s="34"/>
+      <c r="F133" s="32"/>
+      <c r="G133" s="34"/>
+      <c r="H133" s="34">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I133" s="34">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="J133" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K133" s="34"/>
+      <c r="L133" s="32"/>
+      <c r="M133" s="34"/>
+      <c r="N133" s="34"/>
+      <c r="O133" s="34"/>
+      <c r="P133" s="34" t="e">
+        <f>#REF!*8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q133" s="34"/>
+      <c r="R133" s="32"/>
+      <c r="S133" s="34"/>
+      <c r="T133" s="34"/>
+      <c r="U133" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V133" s="34"/>
+      <c r="W133" s="1"/>
+      <c r="X133" s="34"/>
+      <c r="Y133" s="34">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="Z133" s="34">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:26" ht="18">
+      <c r="A134" s="32"/>
+      <c r="B134" s="33"/>
+      <c r="C134" s="32"/>
+      <c r="D134" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E134" s="34"/>
+      <c r="F134" s="32"/>
+      <c r="G134" s="34"/>
+      <c r="H134" s="34">
+        <f t="shared" ref="H134:H135" si="27">IF((D134-E134)&lt;0,0,(D134-E134))</f>
+        <v>0</v>
+      </c>
+      <c r="I134" s="34">
+        <f t="shared" ref="I134:I135" si="28">IF((E134-D134)&lt;0,0,(E134-D134))</f>
+        <v>0</v>
+      </c>
+      <c r="J134" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K134" s="34"/>
+      <c r="L134" s="32"/>
+      <c r="M134" s="34"/>
+      <c r="N134" s="34"/>
+      <c r="O134" s="34"/>
+      <c r="P134" s="34" t="e">
+        <f>#REF!*8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q134" s="34"/>
+      <c r="R134" s="32"/>
+      <c r="S134" s="34"/>
+      <c r="T134" s="34"/>
+      <c r="U134" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V134" s="34"/>
+      <c r="W134" s="32"/>
+      <c r="X134" s="34"/>
+      <c r="Y134" s="34">
+        <f t="shared" ref="Y134:Y135" si="29">IF((U134-V134)&lt;0,0,(U134-V134))</f>
+        <v>0</v>
+      </c>
+      <c r="Z134" s="34">
+        <f t="shared" ref="Z134:Z135" si="30">IF((V134-U134)&lt;0,0,(V134-U134))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:26" ht="18">
+      <c r="A135" s="32"/>
+      <c r="B135" s="33"/>
+      <c r="C135" s="32"/>
+      <c r="D135" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E135" s="34"/>
+      <c r="F135" s="32"/>
+      <c r="G135" s="34"/>
+      <c r="H135" s="34">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="I135" s="34">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="J135" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K135" s="34"/>
+      <c r="L135" s="32"/>
+      <c r="M135" s="34"/>
+      <c r="N135" s="34"/>
+      <c r="O135" s="34"/>
+      <c r="P135" s="34" t="e">
+        <f>#REF!*8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q135" s="34"/>
+      <c r="R135" s="32"/>
+      <c r="S135" s="34"/>
+      <c r="T135" s="34"/>
+      <c r="U135" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="V135" s="34"/>
+      <c r="W135" s="32"/>
+      <c r="X135" s="34"/>
+      <c r="Y135" s="34">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="Z135" s="34">
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 W14:X21 W23:X31 H33:I41 W33:X41 H43:I51 W43:X51 H53:I61 W53:X61 H63:I71 W63:X71 H73:I81 Q73:R81 W73:X81 H83:I91 Q83:R91 W83:X91 H93:I101 Q93:R101 W93:X101 H103:I110 Q103:R110 W103:X110 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D14:F21 D23:F31 D33:F41 D43:F51 D53:F61 D63:F71 D73:F81 D83:F91 D93:F101 D103:F110 D112:F127 D5:F12 K6:L12 K14:L21 K23:L31 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 N5:R12 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 Q63:R71" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 M14:M91 M93:M110" name="SOURCE"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 H33:I41 H43:I51 H53:I61 H63:I71 H73:I81 H83:I91 H93:I101 H103:I110 H112:I127 N127:Q127 V112:W112 H14:I21 H23:I31 H6:I12 Q112:R112 P2:R2 U2:W3 N13:P126 U13:U127 J6:J127 N4:P4 U4 J4 Y4:Z127 N3:R3 X13 D14:F21 D23:F31 D33:F41 D43:F51 D53:F61 D63:F71 D73:F81 D83:F91 D93:F101 D103:F110 D112:F127 D5:F12 K6:L12 K14:L21 K23:L31 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 N5:R12 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 Q63:R71 Q73:R81 Q83:R91 Q93:R101 Q103:R110 Q113:Q126 R113:R127 U5:W12 V14:W21 V23:W31 V33:W41 V43:W51 V53:W61 V63:W71 V73:W81 V83:W91 V93:W101 V103:W110 V113:V127 T4:T127 W113:W133" name="LAS"/>
+    <protectedRange sqref="G2:I3 M2:O2 S93:S110 X2:Z3 G112:G127 M112:M127 S112:S127 X112:X127 G5:G12 M5:M12 S4:S91 X5:X12 G14:G21 M3 X14:X110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 M14:M91 M93:M110 S2:T3" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -14624,26 +14194,23 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 X112:X127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 R73:R81 X83:X91 X93:X101 X14:X21 X5:X12 R112:R127 R103:R110 X112:X127 R83:R91 X103:X110 R93:R101 R63:R71" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W112 W128:W133" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G103:G110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 M14:M91 M93:M110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G103:G110 X14:X110 M93:M110 G5:G12 M5:M12 X5:X12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 M14:M91 S4:S91 S93:S110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F5:F12 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101" xr:uid="{D5D30241-8E27-49BD-930A-61FF5940FF97}">
-      <formula1>"2024,2025,2026"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61" xr:uid="{F7ADBB09-BBC6-48CF-A201-B7FE30E35425}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F5:F12 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 W5:W12 W14:W21 W23:W31 W33:W41 W43:W51 W53:W61 W63:W71 W73:W81 W83:W91 W93:W101 W103:W110 W113:W127" xr:uid="{D5D30241-8E27-49BD-930A-61FF5940FF97}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="J5 P5:P6 V5" calculatedColumn="1"/>
+    <ignoredError sqref="J5 P5:P6 U5" calculatedColumn="1"/>
   </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -14683,38 +14250,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="48" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="49" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="50" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -14727,76 +14294,76 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="G2" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="H2" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="I2" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="J2" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="K2" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="L2" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="M2" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="N2" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="40" t="s">
+      <c r="O2" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="P2" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="Q2" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="Q2" s="24" t="s">
+      <c r="R2" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="S2" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="S2" s="17" t="s">
+      <c r="T2" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="T2" s="17" t="s">
+      <c r="U2" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="U2" s="24" t="s">
+      <c r="V2" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="V2" s="26" t="s">
+      <c r="W2" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="W2" s="26" t="s">
+      <c r="X2" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="Y2" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="Y2" s="41" t="s">
+      <c r="Z2" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="Z2" s="41" t="s">
+      <c r="AA2" s="26" t="s">
         <v>87</v>
-      </c>
-      <c r="AA2" s="26" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="38.25">
@@ -14829,7 +14396,7 @@
         <v>3696</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="5"/>
@@ -15303,7 +14870,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C10" s="1">
         <v>462</v>
@@ -15872,7 +15439,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C19" s="1">
         <v>504</v>
@@ -16512,7 +16079,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C29" s="1">
         <v>555</v>
@@ -17010,7 +16577,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C37" s="5">
         <v>540</v>
@@ -17081,7 +16648,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C38" s="1">
         <v>540</v>
@@ -17223,7 +16790,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C40" s="5">
         <v>540</v>
@@ -17294,7 +16861,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C41" s="1">
         <v>540</v>
@@ -17792,7 +17359,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C49" s="5">
         <v>571</v>
@@ -17863,7 +17430,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C50" s="1">
         <v>571</v>
@@ -18005,7 +17572,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C52" s="5">
         <v>571</v>
@@ -18076,7 +17643,7 @@
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C53" s="1">
         <v>571</v>
@@ -18664,7 +18231,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C61" s="5">
         <v>510</v>
@@ -18747,7 +18314,7 @@
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C62" s="1">
         <v>510</v>
@@ -18901,7 +18468,7 @@
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C64" s="5">
         <v>510</v>
@@ -18984,7 +18551,7 @@
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C65" s="1">
         <v>510</v>
@@ -19062,7 +18629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1"/>
+    <row r="66" spans="1:27" s="7" customFormat="1" ht="15"/>
     <row r="67" spans="1:27" ht="19.5">
       <c r="A67" s="10">
         <v>7</v>
@@ -19091,7 +18658,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="12"/>
-      <c r="L67" s="10"/>
+      <c r="L67" s="12"/>
       <c r="M67" s="12"/>
       <c r="N67" s="12">
         <f t="shared" si="2"/>
@@ -19160,7 +18727,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="12"/>
-      <c r="L68" s="10"/>
+      <c r="L68" s="12"/>
       <c r="M68" s="12"/>
       <c r="N68" s="12">
         <f t="shared" si="2"/>
@@ -19229,7 +18796,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="12"/>
-      <c r="L69" s="10"/>
+      <c r="L69" s="12"/>
       <c r="M69" s="12"/>
       <c r="N69" s="12">
         <f t="shared" si="2"/>
@@ -19298,7 +18865,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="12"/>
-      <c r="L70" s="10"/>
+      <c r="L70" s="12"/>
       <c r="M70" s="12"/>
       <c r="N70" s="12">
         <f t="shared" si="2"/>
@@ -19367,7 +18934,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="12"/>
-      <c r="L71" s="10"/>
+      <c r="L71" s="12"/>
       <c r="M71" s="12"/>
       <c r="N71" s="12">
         <f t="shared" ref="N71:N77" si="14">IF((J71-K71)&lt;0,0,(J71-K71))</f>
@@ -19436,7 +19003,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="12"/>
-      <c r="L72" s="10"/>
+      <c r="L72" s="12"/>
       <c r="M72" s="12"/>
       <c r="N72" s="12">
         <f t="shared" si="14"/>
@@ -19482,7 +19049,7 @@
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C73" s="12"/>
       <c r="D73" s="12">
@@ -19505,7 +19072,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="12"/>
-      <c r="L73" s="10"/>
+      <c r="L73" s="12"/>
       <c r="M73" s="12"/>
       <c r="N73" s="12">
         <f t="shared" si="14"/>
@@ -19551,7 +19118,7 @@
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -19574,7 +19141,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="12"/>
-      <c r="L74" s="10"/>
+      <c r="L74" s="12"/>
       <c r="M74" s="12"/>
       <c r="N74" s="12">
         <f t="shared" si="14"/>
@@ -19643,7 +19210,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="12"/>
-      <c r="L75" s="10"/>
+      <c r="L75" s="12"/>
       <c r="M75" s="12"/>
       <c r="N75" s="12">
         <f t="shared" si="14"/>
@@ -19689,7 +19256,7 @@
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C76" s="12"/>
       <c r="D76" s="12">
@@ -19712,7 +19279,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="12"/>
-      <c r="L76" s="10"/>
+      <c r="L76" s="12"/>
       <c r="M76" s="12"/>
       <c r="N76" s="12">
         <f t="shared" si="14"/>
@@ -19758,7 +19325,7 @@
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -19781,7 +19348,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="12"/>
-      <c r="L77" s="10"/>
+      <c r="L77" s="12"/>
       <c r="M77" s="12"/>
       <c r="N77" s="12">
         <f t="shared" si="14"/>
@@ -19822,7 +19389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
+    <row r="78" spans="1:27" s="7" customFormat="1" ht="15"/>
     <row r="79" spans="1:27" ht="19.149999999999999">
       <c r="A79" s="10">
         <v>8</v>
@@ -20242,7 +19809,7 @@
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C85" s="12"/>
       <c r="D85" s="12">
@@ -20311,7 +19878,7 @@
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -20449,7 +20016,7 @@
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C88" s="12"/>
       <c r="D88" s="12">
@@ -20518,7 +20085,7 @@
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -21002,7 +20569,7 @@
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -21071,7 +20638,7 @@
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -21209,7 +20776,7 @@
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -21278,7 +20845,7 @@
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -21762,7 +21329,7 @@
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="12">
@@ -21831,7 +21398,7 @@
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="12">
@@ -21969,7 +21536,7 @@
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="12">
@@ -22038,7 +21605,7 @@
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="12">
@@ -23169,7 +22736,7 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113 H3:L10 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D103:F113 D115:F122" name="LAS"/>
+    <protectedRange sqref="J2:L2 N3:O10 T3:U10 Z3:AA10 Z12:AA19 Z21:AA29 Z31:AA41 Z43:AA53 Z55:AA65 Z67:AA77 Z79:AA89 Z91:AA101 Z103:AA113 Z115:AA122 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D103:F113 D115:F122 H3:L10 H12:L19 H21:L29 H31:L41 H43:L53 H55:L65 H67:L77 H79:L89 H91:L101 H103:L113 H115:L122 P2:R10 N12:R19 N21:R29 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113 N115:R122 V2:X10 T12:X19 T21:X29 T31:X41 T43:X53 T55:X65 T67:X77 T79:X89 T91:X101 T103:X113 T115:X122" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -23179,14 +22746,11 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 R115:R122 X115:X122 L115:L122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122" xr:uid="{6998821E-F995-40E8-8AFE-164AE8320538}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113 F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
